--- a/AAII_Financials/Quarterly/OTTW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OTTW_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
   <si>
     <t>OTTW</t>
   </si>
@@ -656,140 +656,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42643</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -797,49 +801,49 @@
         <v>3800</v>
       </c>
       <c r="E8" s="3">
-        <v>3600</v>
+        <v>3800</v>
       </c>
       <c r="F8" s="3">
         <v>3600</v>
       </c>
       <c r="G8" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H8" s="3">
         <v>9600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3100</v>
-      </c>
-      <c r="K8" s="3">
-        <v>3200</v>
       </c>
       <c r="L8" s="3">
         <v>3200</v>
       </c>
       <c r="M8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="N8" s="3">
         <v>2900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3200</v>
-      </c>
-      <c r="S8" s="3">
-        <v>3100</v>
       </c>
       <c r="T8" s="3">
         <v>3100</v>
@@ -848,31 +852,31 @@
         <v>3100</v>
       </c>
       <c r="V8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="W8" s="3">
         <v>3000</v>
-      </c>
-      <c r="W8" s="3">
-        <v>2800</v>
       </c>
       <c r="X8" s="3">
         <v>2800</v>
       </c>
       <c r="Y8" s="3">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="Z8" s="3">
         <v>2600</v>
       </c>
       <c r="AA8" s="3">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="AB8" s="3">
         <v>2400</v>
       </c>
       <c r="AC8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AD8" s="3">
         <v>2300</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>2100</v>
       </c>
       <c r="AE8" s="3">
         <v>2100</v>
@@ -880,8 +884,11 @@
       <c r="AF8" s="3">
         <v>2100</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -972,8 +979,11 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1064,8 +1074,11 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1299,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1374,8 +1394,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,8 +1523,9 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1506,28 +1533,28 @@
         <v>1300</v>
       </c>
       <c r="E17" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="F17" s="3">
         <v>1200</v>
       </c>
       <c r="G17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H17" s="3">
         <v>1800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>600</v>
-      </c>
-      <c r="I17" s="3">
-        <v>300</v>
       </c>
       <c r="J17" s="3">
         <v>300</v>
       </c>
       <c r="K17" s="3">
+        <v>300</v>
+      </c>
+      <c r="L17" s="3">
         <v>400</v>
-      </c>
-      <c r="L17" s="3">
-        <v>500</v>
       </c>
       <c r="M17" s="3">
         <v>500</v>
@@ -1536,61 +1563,64 @@
         <v>500</v>
       </c>
       <c r="O17" s="3">
+        <v>500</v>
+      </c>
+      <c r="P17" s="3">
         <v>600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1000</v>
-      </c>
-      <c r="S17" s="3">
-        <v>900</v>
       </c>
       <c r="T17" s="3">
         <v>900</v>
       </c>
       <c r="U17" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="V17" s="3">
         <v>800</v>
       </c>
       <c r="W17" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="X17" s="3">
         <v>600</v>
       </c>
       <c r="Y17" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z17" s="3">
         <v>500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1598,46 +1628,46 @@
         <v>2500</v>
       </c>
       <c r="E18" s="3">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="F18" s="3">
         <v>2400</v>
       </c>
       <c r="G18" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H18" s="3">
         <v>7800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2900</v>
-      </c>
-      <c r="J18" s="3">
-        <v>2800</v>
       </c>
       <c r="K18" s="3">
         <v>2800</v>
       </c>
       <c r="L18" s="3">
+        <v>2800</v>
+      </c>
+      <c r="M18" s="3">
         <v>2700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1900</v>
-      </c>
-      <c r="R18" s="3">
-        <v>2200</v>
       </c>
       <c r="S18" s="3">
         <v>2200</v>
@@ -1646,10 +1676,10 @@
         <v>2200</v>
       </c>
       <c r="U18" s="3">
+        <v>2200</v>
+      </c>
+      <c r="V18" s="3">
         <v>2300</v>
-      </c>
-      <c r="V18" s="3">
-        <v>2200</v>
       </c>
       <c r="W18" s="3">
         <v>2200</v>
@@ -1658,31 +1688,34 @@
         <v>2200</v>
       </c>
       <c r="Y18" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Z18" s="3">
         <v>2100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1900</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>2000</v>
       </c>
       <c r="AC18" s="3">
         <v>2000</v>
       </c>
       <c r="AD18" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AE18" s="3">
         <v>1700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,100 +1748,104 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="E20" s="3">
         <v>-1700</v>
       </c>
       <c r="F20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="G20" s="3">
         <v>-1600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-5100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1600</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-1700</v>
       </c>
       <c r="L20" s="3">
         <v>-1700</v>
       </c>
       <c r="M20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="N20" s="3">
         <v>-1600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-1400</v>
       </c>
       <c r="S20" s="3">
         <v>-1400</v>
       </c>
       <c r="T20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="U20" s="3">
         <v>-1600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>-1500</v>
       </c>
       <c r="AD20" s="3">
         <v>-1500</v>
       </c>
       <c r="AE20" s="3">
-        <v>-1200</v>
+        <v>-1500</v>
       </c>
       <c r="AF20" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1875,32 +1912,35 @@
       <c r="X21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3">
         <v>700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>600</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>700</v>
       </c>
       <c r="AB21" s="3">
         <v>700</v>
       </c>
       <c r="AC21" s="3">
+        <v>700</v>
+      </c>
+      <c r="AD21" s="3">
         <v>600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1991,8 +2031,11 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2000,91 +2043,94 @@
         <v>700</v>
       </c>
       <c r="E23" s="3">
+        <v>700</v>
+      </c>
+      <c r="F23" s="3">
         <v>600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2200</v>
-      </c>
-      <c r="I23" s="3">
-        <v>1200</v>
       </c>
       <c r="J23" s="3">
         <v>1200</v>
       </c>
       <c r="K23" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L23" s="3">
         <v>1100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1000</v>
-      </c>
-      <c r="O23" s="3">
-        <v>1100</v>
       </c>
       <c r="P23" s="3">
         <v>1100</v>
       </c>
       <c r="Q23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="R23" s="3">
         <v>100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>700</v>
-      </c>
-      <c r="T23" s="3">
-        <v>600</v>
       </c>
       <c r="U23" s="3">
         <v>600</v>
       </c>
       <c r="V23" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="W23" s="3">
         <v>800</v>
       </c>
       <c r="X23" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y23" s="3">
         <v>500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>500</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>600</v>
       </c>
       <c r="AB23" s="3">
         <v>600</v>
       </c>
       <c r="AC23" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD23" s="3">
         <v>500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>300</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>600</v>
       </c>
       <c r="AF23" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2098,49 +2144,49 @@
         <v>200</v>
       </c>
       <c r="G24" s="3">
+        <v>200</v>
+      </c>
+      <c r="H24" s="3">
         <v>700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
-      </c>
-      <c r="K24" s="3">
-        <v>300</v>
       </c>
       <c r="L24" s="3">
         <v>300</v>
       </c>
       <c r="M24" s="3">
+        <v>300</v>
+      </c>
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
-      </c>
-      <c r="O24" s="3">
-        <v>300</v>
       </c>
       <c r="P24" s="3">
         <v>300</v>
       </c>
       <c r="Q24" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="R24" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="S24" s="3">
         <v>200</v>
       </c>
       <c r="T24" s="3">
+        <v>200</v>
+      </c>
+      <c r="U24" s="3">
         <v>100</v>
-      </c>
-      <c r="U24" s="3">
-        <v>200</v>
       </c>
       <c r="V24" s="3">
         <v>200</v>
@@ -2149,16 +2195,16 @@
         <v>200</v>
       </c>
       <c r="X24" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1000</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>200</v>
       </c>
       <c r="AB24" s="3">
         <v>200</v>
@@ -2167,16 +2213,19 @@
         <v>200</v>
       </c>
       <c r="AD24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE24" s="3">
         <v>100</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>200</v>
       </c>
       <c r="AF24" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,8 +2316,11 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2276,34 +2328,34 @@
         <v>500</v>
       </c>
       <c r="E26" s="3">
+        <v>500</v>
+      </c>
+      <c r="F26" s="3">
         <v>400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>900</v>
-      </c>
-      <c r="J26" s="3">
-        <v>800</v>
       </c>
       <c r="K26" s="3">
         <v>800</v>
       </c>
       <c r="L26" s="3">
+        <v>800</v>
+      </c>
+      <c r="M26" s="3">
         <v>700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>600</v>
-      </c>
-      <c r="N26" s="3">
-        <v>800</v>
       </c>
       <c r="O26" s="3">
         <v>800</v>
@@ -2312,55 +2364,58 @@
         <v>800</v>
       </c>
       <c r="Q26" s="3">
+        <v>800</v>
+      </c>
+      <c r="R26" s="3">
         <v>100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>500</v>
-      </c>
-      <c r="T26" s="3">
-        <v>400</v>
       </c>
       <c r="U26" s="3">
         <v>400</v>
       </c>
       <c r="V26" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="W26" s="3">
         <v>600</v>
       </c>
       <c r="X26" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y26" s="3">
         <v>400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-500</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>500</v>
       </c>
       <c r="AB26" s="3">
         <v>500</v>
       </c>
       <c r="AC26" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD26" s="3">
         <v>400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>200</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>400</v>
       </c>
       <c r="AF26" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2368,34 +2423,34 @@
         <v>500</v>
       </c>
       <c r="E27" s="3">
+        <v>500</v>
+      </c>
+      <c r="F27" s="3">
         <v>400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>900</v>
-      </c>
-      <c r="J27" s="3">
-        <v>800</v>
       </c>
       <c r="K27" s="3">
         <v>800</v>
       </c>
       <c r="L27" s="3">
+        <v>800</v>
+      </c>
+      <c r="M27" s="3">
         <v>700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>600</v>
-      </c>
-      <c r="N27" s="3">
-        <v>800</v>
       </c>
       <c r="O27" s="3">
         <v>800</v>
@@ -2404,55 +2459,58 @@
         <v>800</v>
       </c>
       <c r="Q27" s="3">
+        <v>800</v>
+      </c>
+      <c r="R27" s="3">
         <v>100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>500</v>
-      </c>
-      <c r="T27" s="3">
-        <v>400</v>
       </c>
       <c r="U27" s="3">
         <v>400</v>
       </c>
       <c r="V27" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="W27" s="3">
         <v>600</v>
       </c>
       <c r="X27" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y27" s="3">
         <v>400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-500</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>500</v>
       </c>
       <c r="AB27" s="3">
         <v>500</v>
       </c>
       <c r="AC27" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD27" s="3">
         <v>400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>200</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>400</v>
       </c>
       <c r="AF27" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,100 +2886,106 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="E32" s="3">
         <v>1700</v>
       </c>
       <c r="F32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G32" s="3">
         <v>1600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>5100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1600</v>
-      </c>
-      <c r="K32" s="3">
-        <v>1700</v>
       </c>
       <c r="L32" s="3">
         <v>1700</v>
       </c>
       <c r="M32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N32" s="3">
         <v>1600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1800</v>
-      </c>
-      <c r="R32" s="3">
-        <v>1400</v>
       </c>
       <c r="S32" s="3">
         <v>1400</v>
       </c>
       <c r="T32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="U32" s="3">
         <v>1600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1400</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>1500</v>
       </c>
       <c r="AD32" s="3">
         <v>1500</v>
       </c>
       <c r="AE32" s="3">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="AF32" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2920,34 +2993,34 @@
         <v>500</v>
       </c>
       <c r="E33" s="3">
+        <v>500</v>
+      </c>
+      <c r="F33" s="3">
         <v>400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>900</v>
-      </c>
-      <c r="J33" s="3">
-        <v>800</v>
       </c>
       <c r="K33" s="3">
         <v>800</v>
       </c>
       <c r="L33" s="3">
+        <v>800</v>
+      </c>
+      <c r="M33" s="3">
         <v>700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>600</v>
-      </c>
-      <c r="N33" s="3">
-        <v>800</v>
       </c>
       <c r="O33" s="3">
         <v>800</v>
@@ -2956,55 +3029,58 @@
         <v>800</v>
       </c>
       <c r="Q33" s="3">
+        <v>800</v>
+      </c>
+      <c r="R33" s="3">
         <v>100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>500</v>
-      </c>
-      <c r="T33" s="3">
-        <v>400</v>
       </c>
       <c r="U33" s="3">
         <v>400</v>
       </c>
       <c r="V33" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="W33" s="3">
         <v>600</v>
       </c>
       <c r="X33" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y33" s="3">
         <v>400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-500</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>500</v>
       </c>
       <c r="AB33" s="3">
         <v>500</v>
       </c>
       <c r="AC33" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD33" s="3">
         <v>400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>200</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>400</v>
       </c>
       <c r="AF33" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,8 +3171,11 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3104,34 +3183,34 @@
         <v>500</v>
       </c>
       <c r="E35" s="3">
+        <v>500</v>
+      </c>
+      <c r="F35" s="3">
         <v>400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>900</v>
-      </c>
-      <c r="J35" s="3">
-        <v>800</v>
       </c>
       <c r="K35" s="3">
         <v>800</v>
       </c>
       <c r="L35" s="3">
+        <v>800</v>
+      </c>
+      <c r="M35" s="3">
         <v>700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>600</v>
-      </c>
-      <c r="N35" s="3">
-        <v>800</v>
       </c>
       <c r="O35" s="3">
         <v>800</v>
@@ -3140,152 +3219,158 @@
         <v>800</v>
       </c>
       <c r="Q35" s="3">
+        <v>800</v>
+      </c>
+      <c r="R35" s="3">
         <v>100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>500</v>
-      </c>
-      <c r="T35" s="3">
-        <v>400</v>
       </c>
       <c r="U35" s="3">
         <v>400</v>
       </c>
       <c r="V35" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="W35" s="3">
         <v>600</v>
       </c>
       <c r="X35" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y35" s="3">
         <v>400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-500</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>500</v>
       </c>
       <c r="AB35" s="3">
         <v>500</v>
       </c>
       <c r="AC35" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD35" s="3">
         <v>400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>200</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>400</v>
       </c>
       <c r="AF35" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42643</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,192 +3438,199 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E41" s="3">
         <v>6300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4100</v>
-      </c>
-      <c r="T41" s="3">
-        <v>4500</v>
       </c>
       <c r="U41" s="3">
         <v>4500</v>
       </c>
       <c r="V41" s="3">
+        <v>4500</v>
+      </c>
+      <c r="W41" s="3">
         <v>2400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E42" s="3">
         <v>3600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>9100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>9300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>18700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>9900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>15200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>12300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>7000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>8600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>7100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>8200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>14300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>10100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>7500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>11900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>7500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>5700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>4800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>4700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>4000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>55900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3628,8 +3721,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,8 +3816,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3812,8 +3911,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3904,8 +4006,11 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3996,8 +4101,11 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4008,7 +4116,7 @@
         <v>6100</v>
       </c>
       <c r="F48" s="3">
-        <v>6200</v>
+        <v>6100</v>
       </c>
       <c r="G48" s="3">
         <v>6200</v>
@@ -4017,16 +4125,16 @@
         <v>6200</v>
       </c>
       <c r="I48" s="3">
-        <v>6300</v>
+        <v>6200</v>
       </c>
       <c r="J48" s="3">
         <v>6300</v>
       </c>
       <c r="K48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="L48" s="3">
         <v>6400</v>
-      </c>
-      <c r="L48" s="3">
-        <v>6300</v>
       </c>
       <c r="M48" s="3">
         <v>6300</v>
@@ -4035,7 +4143,7 @@
         <v>6300</v>
       </c>
       <c r="O48" s="3">
-        <v>6400</v>
+        <v>6300</v>
       </c>
       <c r="P48" s="3">
         <v>6400</v>
@@ -4044,19 +4152,19 @@
         <v>6400</v>
       </c>
       <c r="R48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="S48" s="3">
         <v>6500</v>
-      </c>
-      <c r="S48" s="3">
-        <v>6600</v>
       </c>
       <c r="T48" s="3">
         <v>6600</v>
       </c>
       <c r="U48" s="3">
+        <v>6600</v>
+      </c>
+      <c r="V48" s="3">
         <v>6700</v>
-      </c>
-      <c r="V48" s="3">
-        <v>6600</v>
       </c>
       <c r="W48" s="3">
         <v>6600</v>
@@ -4068,13 +4176,13 @@
         <v>6600</v>
       </c>
       <c r="Z48" s="3">
-        <v>6700</v>
+        <v>6600</v>
       </c>
       <c r="AA48" s="3">
         <v>6700</v>
       </c>
       <c r="AB48" s="3">
-        <v>6800</v>
+        <v>6700</v>
       </c>
       <c r="AC48" s="3">
         <v>6800</v>
@@ -4083,13 +4191,16 @@
         <v>6800</v>
       </c>
       <c r="AE48" s="3">
-        <v>6900</v>
+        <v>6800</v>
       </c>
       <c r="AF48" s="3">
         <v>6900</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4112,7 +4223,7 @@
         <v>700</v>
       </c>
       <c r="J49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="K49" s="3">
         <v>800</v>
@@ -4145,7 +4256,7 @@
         <v>800</v>
       </c>
       <c r="U49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="V49" s="3">
         <v>900</v>
@@ -4163,7 +4274,7 @@
         <v>900</v>
       </c>
       <c r="AA49" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB49" s="3">
         <v>1000</v>
@@ -4178,10 +4289,13 @@
         <v>1000</v>
       </c>
       <c r="AF49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG49" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,37 +4481,40 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2000</v>
-      </c>
-      <c r="J52" s="3">
-        <v>1800</v>
       </c>
       <c r="K52" s="3">
         <v>1800</v>
       </c>
       <c r="L52" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="M52" s="3">
         <v>1700</v>
@@ -4403,19 +4523,19 @@
         <v>1700</v>
       </c>
       <c r="O52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P52" s="3">
         <v>1600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1700</v>
-      </c>
-      <c r="S52" s="3">
-        <v>1800</v>
       </c>
       <c r="T52" s="3">
         <v>1800</v>
@@ -4424,40 +4544,43 @@
         <v>1800</v>
       </c>
       <c r="V52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="W52" s="3">
         <v>1900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2000</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>1900</v>
       </c>
       <c r="Z52" s="3">
         <v>1900</v>
       </c>
       <c r="AA52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AB52" s="3">
         <v>2500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4671,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>365200</v>
+      </c>
+      <c r="E54" s="3">
         <v>366800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>369100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>357800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>359200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>343300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>348800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>342500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>343200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>330500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>323400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>307600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>310600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>312200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>307100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>300500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>304200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>301600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>289500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>292800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>277700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>273800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>268000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>255400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>245700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>239000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>236400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>230200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>276100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>216700</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,8 +4838,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4717,16 +4848,16 @@
         <v>300</v>
       </c>
       <c r="E57" s="3">
+        <v>300</v>
+      </c>
+      <c r="F57" s="3">
         <v>200</v>
-      </c>
-      <c r="F57" s="3">
-        <v>100</v>
       </c>
       <c r="G57" s="3">
         <v>100</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I57" s="3">
         <v>0</v>
@@ -4738,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="L57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M57" s="3">
         <v>100</v>
@@ -4756,7 +4887,7 @@
         <v>100</v>
       </c>
       <c r="R57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
@@ -4800,8 +4931,11 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4892,8 +5026,11 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4984,8 +5121,11 @@
       <c r="AF59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5076,22 +5216,25 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1900</v>
-      </c>
-      <c r="E61" s="3">
-        <v>2100</v>
       </c>
       <c r="F61" s="3">
         <v>2100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -5168,8 +5311,11 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5260,8 +5406,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5691,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>322500</v>
+      </c>
+      <c r="E66" s="3">
         <v>323800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>326100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>314600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>316100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>298300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>301700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>294500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>294400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>281700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>274800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>258400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>261700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>262600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>258300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>249800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>253900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>251000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>236600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>240000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>225100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>221400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>215500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>202300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>191700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>185400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>183300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>177400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>243700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>184700</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6201,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E72" s="3">
         <v>21800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>21500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>21900</v>
-      </c>
-      <c r="G72" s="3">
-        <v>21600</v>
       </c>
       <c r="H72" s="3">
         <v>21600</v>
       </c>
       <c r="I72" s="3">
+        <v>21600</v>
+      </c>
+      <c r="J72" s="3">
         <v>21100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>20500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>20100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>19500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>19000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>19500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>18800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>18300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>17800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>18900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>18500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>18100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>19100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>18900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>18500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>18000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>17800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>17700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>18300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>18000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>17700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>17500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>17200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6581,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>42700</v>
+      </c>
+      <c r="E76" s="3">
         <v>42900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>43000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>43300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>43100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>45000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>47100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>48000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>48900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>48800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>48600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>49200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>48900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>49600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>48800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>50700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>50300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>50600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>52900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>52800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>52600</v>
-      </c>
-      <c r="X76" s="3">
-        <v>52500</v>
       </c>
       <c r="Y76" s="3">
         <v>52500</v>
       </c>
       <c r="Z76" s="3">
+        <v>52500</v>
+      </c>
+      <c r="AA76" s="3">
         <v>53100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>54000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>53700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>53100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>52700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>32400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>32000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,105 +6771,111 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42643</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6688,34 +6883,34 @@
         <v>500</v>
       </c>
       <c r="E81" s="3">
+        <v>500</v>
+      </c>
+      <c r="F81" s="3">
         <v>400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>900</v>
-      </c>
-      <c r="J81" s="3">
-        <v>800</v>
       </c>
       <c r="K81" s="3">
         <v>800</v>
       </c>
       <c r="L81" s="3">
+        <v>800</v>
+      </c>
+      <c r="M81" s="3">
         <v>700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>600</v>
-      </c>
-      <c r="N81" s="3">
-        <v>800</v>
       </c>
       <c r="O81" s="3">
         <v>800</v>
@@ -6724,55 +6919,58 @@
         <v>800</v>
       </c>
       <c r="Q81" s="3">
+        <v>800</v>
+      </c>
+      <c r="R81" s="3">
         <v>100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>500</v>
-      </c>
-      <c r="T81" s="3">
-        <v>400</v>
       </c>
       <c r="U81" s="3">
         <v>400</v>
       </c>
       <c r="V81" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="W81" s="3">
         <v>600</v>
       </c>
       <c r="X81" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y81" s="3">
         <v>400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-500</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>500</v>
       </c>
       <c r="AB81" s="3">
         <v>500</v>
       </c>
       <c r="AC81" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD81" s="3">
         <v>400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>200</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>400</v>
       </c>
       <c r="AF81" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7003,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6870,11 +7069,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>100</v>
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z83" s="3">
         <v>100</v>
@@ -6897,8 +7096,11 @@
       <c r="AF83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,8 +7571,11 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7422,35 +7639,38 @@
       <c r="W89" s="3">
         <v>0</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z89" s="3">
         <v>1000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-200</v>
       </c>
-      <c r="AF89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7703,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7548,11 +7769,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -7575,8 +7796,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,8 +7986,11 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7824,35 +8054,38 @@
       <c r="W94" s="3">
         <v>0</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y94" s="3">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-13700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-10000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-7100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>45300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-57500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7957,7 +8191,7 @@
         <v>0</v>
       </c>
       <c r="Z96" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA96" s="3">
         <v>-100</v>
@@ -7969,7 +8203,7 @@
         <v>-100</v>
       </c>
       <c r="AD96" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE96" s="3">
         <v>0</v>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,8 +8496,11 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8318,35 +8564,38 @@
       <c r="W100" s="3">
         <v>0</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z100" s="3">
         <v>12100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>9500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>6700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>5400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-46300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>59600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,8 +8686,11 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8502,31 +8754,34 @@
       <c r="W102" s="3">
         <v>0</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OTTW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OTTW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
   <si>
     <t>OTTW</t>
   </si>
@@ -656,197 +656,200 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="E8" s="3">
         <v>3800</v>
       </c>
       <c r="F8" s="3">
-        <v>3600</v>
+        <v>3800</v>
       </c>
       <c r="G8" s="3">
         <v>3600</v>
       </c>
       <c r="H8" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I8" s="3">
         <v>9600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3100</v>
-      </c>
-      <c r="L8" s="3">
-        <v>3200</v>
       </c>
       <c r="M8" s="3">
         <v>3200</v>
       </c>
       <c r="N8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="O8" s="3">
         <v>2900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3200</v>
-      </c>
-      <c r="T8" s="3">
-        <v>3100</v>
       </c>
       <c r="U8" s="3">
         <v>3100</v>
@@ -855,31 +858,31 @@
         <v>3100</v>
       </c>
       <c r="W8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="X8" s="3">
         <v>3000</v>
-      </c>
-      <c r="X8" s="3">
-        <v>2800</v>
       </c>
       <c r="Y8" s="3">
         <v>2800</v>
       </c>
       <c r="Z8" s="3">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="AA8" s="3">
         <v>2600</v>
       </c>
       <c r="AB8" s="3">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="AC8" s="3">
         <v>2400</v>
       </c>
       <c r="AD8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AE8" s="3">
         <v>2300</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>2100</v>
       </c>
       <c r="AF8" s="3">
         <v>2100</v>
@@ -887,8 +890,11 @@
       <c r="AG8" s="3">
         <v>2100</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -982,8 +988,11 @@
       <c r="AG9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1077,8 +1086,11 @@
       <c r="AG10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1207,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,8 +1318,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1397,8 +1416,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1492,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,40 +1549,41 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="E17" s="3">
         <v>1300</v>
       </c>
       <c r="F17" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="G17" s="3">
         <v>1200</v>
       </c>
       <c r="H17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I17" s="3">
         <v>1800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>600</v>
-      </c>
-      <c r="J17" s="3">
-        <v>300</v>
       </c>
       <c r="K17" s="3">
         <v>300</v>
       </c>
       <c r="L17" s="3">
+        <v>300</v>
+      </c>
+      <c r="M17" s="3">
         <v>400</v>
-      </c>
-      <c r="M17" s="3">
-        <v>500</v>
       </c>
       <c r="N17" s="3">
         <v>500</v>
@@ -1566,111 +1592,114 @@
         <v>500</v>
       </c>
       <c r="P17" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q17" s="3">
         <v>600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1000</v>
-      </c>
-      <c r="T17" s="3">
-        <v>900</v>
       </c>
       <c r="U17" s="3">
         <v>900</v>
       </c>
       <c r="V17" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="W17" s="3">
         <v>800</v>
       </c>
       <c r="X17" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="Y17" s="3">
         <v>600</v>
       </c>
       <c r="Z17" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA17" s="3">
         <v>500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="E18" s="3">
         <v>2500</v>
       </c>
       <c r="F18" s="3">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="G18" s="3">
         <v>2400</v>
       </c>
       <c r="H18" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I18" s="3">
         <v>7800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2900</v>
-      </c>
-      <c r="K18" s="3">
-        <v>2800</v>
       </c>
       <c r="L18" s="3">
         <v>2800</v>
       </c>
       <c r="M18" s="3">
+        <v>2800</v>
+      </c>
+      <c r="N18" s="3">
         <v>2700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1900</v>
-      </c>
-      <c r="S18" s="3">
-        <v>2200</v>
       </c>
       <c r="T18" s="3">
         <v>2200</v>
@@ -1679,10 +1708,10 @@
         <v>2200</v>
       </c>
       <c r="V18" s="3">
+        <v>2200</v>
+      </c>
+      <c r="W18" s="3">
         <v>2300</v>
-      </c>
-      <c r="W18" s="3">
-        <v>2200</v>
       </c>
       <c r="X18" s="3">
         <v>2200</v>
@@ -1691,31 +1720,34 @@
         <v>2200</v>
       </c>
       <c r="Z18" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AA18" s="3">
         <v>2100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1900</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>2000</v>
       </c>
       <c r="AD18" s="3">
         <v>2000</v>
       </c>
       <c r="AE18" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AF18" s="3">
         <v>1700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,103 +1781,107 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-1700</v>
       </c>
       <c r="F20" s="3">
         <v>-1700</v>
       </c>
       <c r="G20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="H20" s="3">
         <v>-1600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-5100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1600</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-1700</v>
       </c>
       <c r="M20" s="3">
         <v>-1700</v>
       </c>
       <c r="N20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="O20" s="3">
         <v>-1600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-1400</v>
       </c>
       <c r="T20" s="3">
         <v>-1400</v>
       </c>
       <c r="U20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="V20" s="3">
         <v>-1600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>-1500</v>
       </c>
       <c r="AE20" s="3">
         <v>-1500</v>
       </c>
       <c r="AF20" s="3">
-        <v>-1200</v>
+        <v>-1500</v>
       </c>
       <c r="AG20" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1915,32 +1951,35 @@
       <c r="Y21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA21" s="3">
         <v>700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>600</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>700</v>
       </c>
       <c r="AC21" s="3">
         <v>700</v>
       </c>
       <c r="AD21" s="3">
+        <v>700</v>
+      </c>
+      <c r="AE21" s="3">
         <v>600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2034,108 +2073,114 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="E23" s="3">
         <v>700</v>
       </c>
       <c r="F23" s="3">
+        <v>700</v>
+      </c>
+      <c r="G23" s="3">
         <v>600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2200</v>
-      </c>
-      <c r="J23" s="3">
-        <v>1200</v>
       </c>
       <c r="K23" s="3">
         <v>1200</v>
       </c>
       <c r="L23" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M23" s="3">
         <v>1100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1000</v>
-      </c>
-      <c r="P23" s="3">
-        <v>1100</v>
       </c>
       <c r="Q23" s="3">
         <v>1100</v>
       </c>
       <c r="R23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S23" s="3">
         <v>100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>700</v>
-      </c>
-      <c r="U23" s="3">
-        <v>600</v>
       </c>
       <c r="V23" s="3">
         <v>600</v>
       </c>
       <c r="W23" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="X23" s="3">
         <v>800</v>
       </c>
       <c r="Y23" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z23" s="3">
         <v>500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>500</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>600</v>
       </c>
       <c r="AC23" s="3">
         <v>600</v>
       </c>
       <c r="AD23" s="3">
+        <v>600</v>
+      </c>
+      <c r="AE23" s="3">
         <v>500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>300</v>
-      </c>
-      <c r="AF23" s="3">
-        <v>600</v>
       </c>
       <c r="AG23" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
         <v>200</v>
@@ -2147,49 +2192,49 @@
         <v>200</v>
       </c>
       <c r="H24" s="3">
+        <v>200</v>
+      </c>
+      <c r="I24" s="3">
         <v>700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>400</v>
-      </c>
-      <c r="L24" s="3">
-        <v>300</v>
       </c>
       <c r="M24" s="3">
         <v>300</v>
       </c>
       <c r="N24" s="3">
+        <v>300</v>
+      </c>
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
-      </c>
-      <c r="P24" s="3">
-        <v>300</v>
       </c>
       <c r="Q24" s="3">
         <v>300</v>
       </c>
       <c r="R24" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="S24" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="T24" s="3">
         <v>200</v>
       </c>
       <c r="U24" s="3">
+        <v>200</v>
+      </c>
+      <c r="V24" s="3">
         <v>100</v>
-      </c>
-      <c r="V24" s="3">
-        <v>200</v>
       </c>
       <c r="W24" s="3">
         <v>200</v>
@@ -2198,16 +2243,16 @@
         <v>200</v>
       </c>
       <c r="Y24" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1000</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>200</v>
       </c>
       <c r="AC24" s="3">
         <v>200</v>
@@ -2216,16 +2261,19 @@
         <v>200</v>
       </c>
       <c r="AE24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF24" s="3">
         <v>100</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>200</v>
       </c>
       <c r="AG24" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,46 +2367,49 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E26" s="3">
         <v>500</v>
       </c>
       <c r="F26" s="3">
+        <v>500</v>
+      </c>
+      <c r="G26" s="3">
         <v>400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>900</v>
-      </c>
-      <c r="K26" s="3">
-        <v>800</v>
       </c>
       <c r="L26" s="3">
         <v>800</v>
       </c>
       <c r="M26" s="3">
+        <v>800</v>
+      </c>
+      <c r="N26" s="3">
         <v>700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>600</v>
-      </c>
-      <c r="O26" s="3">
-        <v>800</v>
       </c>
       <c r="P26" s="3">
         <v>800</v>
@@ -2367,93 +2418,96 @@
         <v>800</v>
       </c>
       <c r="R26" s="3">
+        <v>800</v>
+      </c>
+      <c r="S26" s="3">
         <v>100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>500</v>
-      </c>
-      <c r="U26" s="3">
-        <v>400</v>
       </c>
       <c r="V26" s="3">
         <v>400</v>
       </c>
       <c r="W26" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="X26" s="3">
         <v>600</v>
       </c>
       <c r="Y26" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z26" s="3">
         <v>400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-500</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>500</v>
       </c>
       <c r="AC26" s="3">
         <v>500</v>
       </c>
       <c r="AD26" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE26" s="3">
         <v>400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>200</v>
-      </c>
-      <c r="AF26" s="3">
-        <v>400</v>
       </c>
       <c r="AG26" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E27" s="3">
         <v>500</v>
       </c>
       <c r="F27" s="3">
+        <v>500</v>
+      </c>
+      <c r="G27" s="3">
         <v>400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>900</v>
-      </c>
-      <c r="K27" s="3">
-        <v>800</v>
       </c>
       <c r="L27" s="3">
         <v>800</v>
       </c>
       <c r="M27" s="3">
+        <v>800</v>
+      </c>
+      <c r="N27" s="3">
         <v>700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>600</v>
-      </c>
-      <c r="O27" s="3">
-        <v>800</v>
       </c>
       <c r="P27" s="3">
         <v>800</v>
@@ -2462,55 +2516,58 @@
         <v>800</v>
       </c>
       <c r="R27" s="3">
+        <v>800</v>
+      </c>
+      <c r="S27" s="3">
         <v>100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>500</v>
-      </c>
-      <c r="U27" s="3">
-        <v>400</v>
       </c>
       <c r="V27" s="3">
         <v>400</v>
       </c>
       <c r="W27" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="X27" s="3">
         <v>600</v>
       </c>
       <c r="Y27" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z27" s="3">
         <v>400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-500</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>500</v>
       </c>
       <c r="AC27" s="3">
         <v>500</v>
       </c>
       <c r="AD27" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE27" s="3">
         <v>400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>200</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>400</v>
       </c>
       <c r="AG27" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2699,8 +2759,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,141 +2955,147 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E32" s="3">
         <v>1800</v>
-      </c>
-      <c r="E32" s="3">
-        <v>1700</v>
       </c>
       <c r="F32" s="3">
         <v>1700</v>
       </c>
       <c r="G32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H32" s="3">
         <v>1600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>5100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1600</v>
-      </c>
-      <c r="L32" s="3">
-        <v>1700</v>
       </c>
       <c r="M32" s="3">
         <v>1700</v>
       </c>
       <c r="N32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O32" s="3">
         <v>1600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1800</v>
-      </c>
-      <c r="S32" s="3">
-        <v>1400</v>
       </c>
       <c r="T32" s="3">
         <v>1400</v>
       </c>
       <c r="U32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="V32" s="3">
         <v>1600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1400</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>1500</v>
       </c>
       <c r="AE32" s="3">
         <v>1500</v>
       </c>
       <c r="AF32" s="3">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="AG32" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E33" s="3">
         <v>500</v>
       </c>
       <c r="F33" s="3">
+        <v>500</v>
+      </c>
+      <c r="G33" s="3">
         <v>400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>900</v>
-      </c>
-      <c r="K33" s="3">
-        <v>800</v>
       </c>
       <c r="L33" s="3">
         <v>800</v>
       </c>
       <c r="M33" s="3">
+        <v>800</v>
+      </c>
+      <c r="N33" s="3">
         <v>700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>600</v>
-      </c>
-      <c r="O33" s="3">
-        <v>800</v>
       </c>
       <c r="P33" s="3">
         <v>800</v>
@@ -3032,55 +3104,58 @@
         <v>800</v>
       </c>
       <c r="R33" s="3">
+        <v>800</v>
+      </c>
+      <c r="S33" s="3">
         <v>100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>500</v>
-      </c>
-      <c r="U33" s="3">
-        <v>400</v>
       </c>
       <c r="V33" s="3">
         <v>400</v>
       </c>
       <c r="W33" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="X33" s="3">
         <v>600</v>
       </c>
       <c r="Y33" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z33" s="3">
         <v>400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-500</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>500</v>
       </c>
       <c r="AC33" s="3">
         <v>500</v>
       </c>
       <c r="AD33" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE33" s="3">
         <v>400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>200</v>
-      </c>
-      <c r="AF33" s="3">
-        <v>400</v>
       </c>
       <c r="AG33" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,46 +3249,49 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E35" s="3">
         <v>500</v>
       </c>
       <c r="F35" s="3">
+        <v>500</v>
+      </c>
+      <c r="G35" s="3">
         <v>400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>900</v>
-      </c>
-      <c r="K35" s="3">
-        <v>800</v>
       </c>
       <c r="L35" s="3">
         <v>800</v>
       </c>
       <c r="M35" s="3">
+        <v>800</v>
+      </c>
+      <c r="N35" s="3">
         <v>700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>600</v>
-      </c>
-      <c r="O35" s="3">
-        <v>800</v>
       </c>
       <c r="P35" s="3">
         <v>800</v>
@@ -3222,155 +3300,161 @@
         <v>800</v>
       </c>
       <c r="R35" s="3">
+        <v>800</v>
+      </c>
+      <c r="S35" s="3">
         <v>100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>500</v>
-      </c>
-      <c r="U35" s="3">
-        <v>400</v>
       </c>
       <c r="V35" s="3">
         <v>400</v>
       </c>
       <c r="W35" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="X35" s="3">
         <v>600</v>
       </c>
       <c r="Y35" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z35" s="3">
         <v>400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-500</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>500</v>
       </c>
       <c r="AC35" s="3">
         <v>500</v>
       </c>
       <c r="AD35" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE35" s="3">
         <v>400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>200</v>
-      </c>
-      <c r="AF35" s="3">
-        <v>400</v>
       </c>
       <c r="AG35" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,198 +3524,205 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E41" s="3">
         <v>4500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4100</v>
-      </c>
-      <c r="U41" s="3">
-        <v>4500</v>
       </c>
       <c r="V41" s="3">
         <v>4500</v>
       </c>
       <c r="W41" s="3">
+        <v>4500</v>
+      </c>
+      <c r="X41" s="3">
         <v>2400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E42" s="3">
         <v>8400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>9300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>18700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>9900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>15200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>12300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>7000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>8600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>7100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>8200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>14300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>10100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>7500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>11900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>7500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>5700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>4800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>4700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>4000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>55900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3724,8 +3816,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3819,8 +3914,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3914,8 +4012,11 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4009,8 +4110,11 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4104,13 +4208,16 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6100</v>
+        <v>6000</v>
       </c>
       <c r="E48" s="3">
         <v>6100</v>
@@ -4119,7 +4226,7 @@
         <v>6100</v>
       </c>
       <c r="G48" s="3">
-        <v>6200</v>
+        <v>6100</v>
       </c>
       <c r="H48" s="3">
         <v>6200</v>
@@ -4128,16 +4235,16 @@
         <v>6200</v>
       </c>
       <c r="J48" s="3">
-        <v>6300</v>
+        <v>6200</v>
       </c>
       <c r="K48" s="3">
         <v>6300</v>
       </c>
       <c r="L48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="M48" s="3">
         <v>6400</v>
-      </c>
-      <c r="M48" s="3">
-        <v>6300</v>
       </c>
       <c r="N48" s="3">
         <v>6300</v>
@@ -4146,7 +4253,7 @@
         <v>6300</v>
       </c>
       <c r="P48" s="3">
-        <v>6400</v>
+        <v>6300</v>
       </c>
       <c r="Q48" s="3">
         <v>6400</v>
@@ -4155,19 +4262,19 @@
         <v>6400</v>
       </c>
       <c r="S48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="T48" s="3">
         <v>6500</v>
-      </c>
-      <c r="T48" s="3">
-        <v>6600</v>
       </c>
       <c r="U48" s="3">
         <v>6600</v>
       </c>
       <c r="V48" s="3">
+        <v>6600</v>
+      </c>
+      <c r="W48" s="3">
         <v>6700</v>
-      </c>
-      <c r="W48" s="3">
-        <v>6600</v>
       </c>
       <c r="X48" s="3">
         <v>6600</v>
@@ -4179,13 +4286,13 @@
         <v>6600</v>
       </c>
       <c r="AA48" s="3">
-        <v>6700</v>
+        <v>6600</v>
       </c>
       <c r="AB48" s="3">
         <v>6700</v>
       </c>
       <c r="AC48" s="3">
-        <v>6800</v>
+        <v>6700</v>
       </c>
       <c r="AD48" s="3">
         <v>6800</v>
@@ -4194,13 +4301,16 @@
         <v>6800</v>
       </c>
       <c r="AF48" s="3">
-        <v>6900</v>
+        <v>6800</v>
       </c>
       <c r="AG48" s="3">
         <v>6900</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4226,7 +4336,7 @@
         <v>700</v>
       </c>
       <c r="K49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="L49" s="3">
         <v>800</v>
@@ -4259,7 +4369,7 @@
         <v>800</v>
       </c>
       <c r="V49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="W49" s="3">
         <v>900</v>
@@ -4277,7 +4387,7 @@
         <v>900</v>
       </c>
       <c r="AB49" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AC49" s="3">
         <v>1000</v>
@@ -4292,10 +4402,13 @@
         <v>1000</v>
       </c>
       <c r="AG49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AH49" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,40 +4600,43 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E52" s="3">
         <v>3000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2000</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1800</v>
       </c>
       <c r="L52" s="3">
         <v>1800</v>
       </c>
       <c r="M52" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="N52" s="3">
         <v>1700</v>
@@ -4526,19 +4645,19 @@
         <v>1700</v>
       </c>
       <c r="P52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q52" s="3">
         <v>1600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1700</v>
-      </c>
-      <c r="T52" s="3">
-        <v>1800</v>
       </c>
       <c r="U52" s="3">
         <v>1800</v>
@@ -4547,40 +4666,43 @@
         <v>1800</v>
       </c>
       <c r="W52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="X52" s="3">
         <v>1900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2000</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>1900</v>
       </c>
       <c r="AA52" s="3">
         <v>1900</v>
       </c>
       <c r="AB52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AC52" s="3">
         <v>2500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>363900</v>
+      </c>
+      <c r="E54" s="3">
         <v>365200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>366800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>369100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>357800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>359200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>343300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>348800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>342500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>343200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>330500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>323400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>307600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>310600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>312200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>307100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>300500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>304200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>301600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>289500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>292800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>277700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>273800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>268000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>255400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>245700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>239000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>236400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>230200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>276100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>216700</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,8 +4968,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4851,16 +4981,16 @@
         <v>300</v>
       </c>
       <c r="F57" s="3">
+        <v>300</v>
+      </c>
+      <c r="G57" s="3">
         <v>200</v>
-      </c>
-      <c r="G57" s="3">
-        <v>100</v>
       </c>
       <c r="H57" s="3">
         <v>100</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J57" s="3">
         <v>0</v>
@@ -4872,7 +5002,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N57" s="3">
         <v>100</v>
@@ -4890,7 +5020,7 @@
         <v>100</v>
       </c>
       <c r="S57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T57" s="3">
         <v>0</v>
@@ -4934,8 +5064,11 @@
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5029,8 +5162,11 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5124,8 +5260,11 @@
       <c r="AG59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5219,8 +5358,11 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5228,16 +5370,16 @@
         <v>1700</v>
       </c>
       <c r="E61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F61" s="3">
         <v>1900</v>
-      </c>
-      <c r="F61" s="3">
-        <v>2100</v>
       </c>
       <c r="G61" s="3">
         <v>2100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -5314,8 +5456,11 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5409,8 +5554,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>320600</v>
+      </c>
+      <c r="E66" s="3">
         <v>322500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>323800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>326100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>314600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>316100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>298300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>301700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>294500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>294400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>281700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>274800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>258400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>261700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>262600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>258300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>249800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>253900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>251000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>236600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>240000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>225100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>221400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>215500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>202300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>191700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>185400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>183300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>177400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>243700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>184700</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E72" s="3">
         <v>21900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>21800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>21500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>21900</v>
-      </c>
-      <c r="H72" s="3">
-        <v>21600</v>
       </c>
       <c r="I72" s="3">
         <v>21600</v>
       </c>
       <c r="J72" s="3">
+        <v>21600</v>
+      </c>
+      <c r="K72" s="3">
         <v>21100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>20500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>20100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>19500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>19000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>19500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>18800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>18300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>18900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>18500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>18100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>19100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>18900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>18500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>18000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>17800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>17700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>18300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>18000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>17700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>17500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>17200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>43300</v>
+      </c>
+      <c r="E76" s="3">
         <v>42700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>42900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>43000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>43300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>43100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>45000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>47100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>48000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>48900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>48800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>48600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>49200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>48900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>49600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>48800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>50700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>50300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>50600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>52900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>52800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>52600</v>
-      </c>
-      <c r="Y76" s="3">
-        <v>52500</v>
       </c>
       <c r="Z76" s="3">
         <v>52500</v>
       </c>
       <c r="AA76" s="3">
+        <v>52500</v>
+      </c>
+      <c r="AB76" s="3">
         <v>53100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>54000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>53700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>53100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>52700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>32400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>32000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,146 +6962,152 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E81" s="3">
         <v>500</v>
       </c>
       <c r="F81" s="3">
+        <v>500</v>
+      </c>
+      <c r="G81" s="3">
         <v>400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>900</v>
-      </c>
-      <c r="K81" s="3">
-        <v>800</v>
       </c>
       <c r="L81" s="3">
         <v>800</v>
       </c>
       <c r="M81" s="3">
+        <v>800</v>
+      </c>
+      <c r="N81" s="3">
         <v>700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>600</v>
-      </c>
-      <c r="O81" s="3">
-        <v>800</v>
       </c>
       <c r="P81" s="3">
         <v>800</v>
@@ -6922,55 +7116,58 @@
         <v>800</v>
       </c>
       <c r="R81" s="3">
+        <v>800</v>
+      </c>
+      <c r="S81" s="3">
         <v>100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>500</v>
-      </c>
-      <c r="U81" s="3">
-        <v>400</v>
       </c>
       <c r="V81" s="3">
         <v>400</v>
       </c>
       <c r="W81" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="X81" s="3">
         <v>600</v>
       </c>
       <c r="Y81" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z81" s="3">
         <v>400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-500</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>500</v>
       </c>
       <c r="AC81" s="3">
         <v>500</v>
       </c>
       <c r="AD81" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE81" s="3">
         <v>400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>200</v>
-      </c>
-      <c r="AF81" s="3">
-        <v>400</v>
       </c>
       <c r="AG81" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7072,11 +7270,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>100</v>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA83" s="3">
         <v>100</v>
@@ -7099,8 +7297,11 @@
       <c r="AG83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,8 +7787,11 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7642,35 +7858,38 @@
       <c r="X89" s="3">
         <v>0</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA89" s="3">
         <v>1000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-200</v>
       </c>
-      <c r="AG89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,8 +7923,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7772,11 +7992,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
@@ -7799,8 +8019,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,8 +8215,11 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8057,35 +8286,38 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-13700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-10000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-7100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>45300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-57500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8194,7 +8427,7 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB96" s="3">
         <v>-100</v>
@@ -8206,7 +8439,7 @@
         <v>-100</v>
       </c>
       <c r="AE96" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AF96" s="3">
         <v>0</v>
@@ -8214,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,8 +8741,11 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8567,35 +8812,38 @@
       <c r="X100" s="3">
         <v>0</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA100" s="3">
         <v>12100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>9500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>6700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>5400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-46300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>59600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8689,8 +8937,11 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8757,31 +9008,34 @@
       <c r="X102" s="3">
         <v>0</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OTTW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OTTW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
   <si>
     <t>OTTW</t>
   </si>
@@ -656,147 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -804,55 +808,55 @@
         <v>3900</v>
       </c>
       <c r="E8" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="F8" s="3">
         <v>3800</v>
       </c>
       <c r="G8" s="3">
-        <v>3600</v>
+        <v>3800</v>
       </c>
       <c r="H8" s="3">
         <v>3600</v>
       </c>
       <c r="I8" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J8" s="3">
         <v>9600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3100</v>
-      </c>
-      <c r="M8" s="3">
-        <v>3200</v>
       </c>
       <c r="N8" s="3">
         <v>3200</v>
       </c>
       <c r="O8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="P8" s="3">
         <v>2900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3200</v>
-      </c>
-      <c r="U8" s="3">
-        <v>3100</v>
       </c>
       <c r="V8" s="3">
         <v>3100</v>
@@ -861,31 +865,31 @@
         <v>3100</v>
       </c>
       <c r="X8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Y8" s="3">
         <v>3000</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>2800</v>
       </c>
       <c r="Z8" s="3">
         <v>2800</v>
       </c>
       <c r="AA8" s="3">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="AB8" s="3">
         <v>2600</v>
       </c>
       <c r="AC8" s="3">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="AD8" s="3">
         <v>2400</v>
       </c>
       <c r="AE8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AF8" s="3">
         <v>2300</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>2100</v>
       </c>
       <c r="AG8" s="3">
         <v>2100</v>
@@ -893,8 +897,11 @@
       <c r="AH8" s="3">
         <v>2100</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -991,8 +998,11 @@
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1089,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,43 +1576,44 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1600</v>
-      </c>
-      <c r="E17" s="3">
-        <v>1300</v>
       </c>
       <c r="F17" s="3">
         <v>1300</v>
       </c>
       <c r="G17" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="H17" s="3">
         <v>1200</v>
       </c>
       <c r="I17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J17" s="3">
         <v>1800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>600</v>
-      </c>
-      <c r="K17" s="3">
-        <v>300</v>
       </c>
       <c r="L17" s="3">
         <v>300</v>
       </c>
       <c r="M17" s="3">
+        <v>300</v>
+      </c>
+      <c r="N17" s="3">
         <v>400</v>
-      </c>
-      <c r="N17" s="3">
-        <v>500</v>
       </c>
       <c r="O17" s="3">
         <v>500</v>
@@ -1595,114 +1622,117 @@
         <v>500</v>
       </c>
       <c r="Q17" s="3">
+        <v>500</v>
+      </c>
+      <c r="R17" s="3">
         <v>600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1000</v>
-      </c>
-      <c r="U17" s="3">
-        <v>900</v>
       </c>
       <c r="V17" s="3">
         <v>900</v>
       </c>
       <c r="W17" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="X17" s="3">
         <v>800</v>
       </c>
       <c r="Y17" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="Z17" s="3">
         <v>600</v>
       </c>
       <c r="AA17" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB17" s="3">
         <v>500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E18" s="3">
         <v>2300</v>
-      </c>
-      <c r="E18" s="3">
-        <v>2500</v>
       </c>
       <c r="F18" s="3">
         <v>2500</v>
       </c>
       <c r="G18" s="3">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="H18" s="3">
         <v>2400</v>
       </c>
       <c r="I18" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J18" s="3">
         <v>7800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2900</v>
-      </c>
-      <c r="L18" s="3">
-        <v>2800</v>
       </c>
       <c r="M18" s="3">
         <v>2800</v>
       </c>
       <c r="N18" s="3">
+        <v>2800</v>
+      </c>
+      <c r="O18" s="3">
         <v>2700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1900</v>
-      </c>
-      <c r="T18" s="3">
-        <v>2200</v>
       </c>
       <c r="U18" s="3">
         <v>2200</v>
@@ -1711,10 +1741,10 @@
         <v>2200</v>
       </c>
       <c r="W18" s="3">
+        <v>2200</v>
+      </c>
+      <c r="X18" s="3">
         <v>2300</v>
-      </c>
-      <c r="X18" s="3">
-        <v>2200</v>
       </c>
       <c r="Y18" s="3">
         <v>2200</v>
@@ -1723,31 +1753,34 @@
         <v>2200</v>
       </c>
       <c r="AA18" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AB18" s="3">
         <v>2100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1900</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>2000</v>
       </c>
       <c r="AE18" s="3">
         <v>2000</v>
       </c>
       <c r="AF18" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AG18" s="3">
         <v>1700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,106 +1815,110 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-1700</v>
       </c>
       <c r="G20" s="3">
         <v>-1700</v>
       </c>
       <c r="H20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I20" s="3">
         <v>-1600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1600</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-1700</v>
       </c>
       <c r="N20" s="3">
         <v>-1700</v>
       </c>
       <c r="O20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="P20" s="3">
         <v>-1600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-1400</v>
       </c>
       <c r="U20" s="3">
         <v>-1400</v>
       </c>
       <c r="V20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="W20" s="3">
         <v>-1600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>-1500</v>
       </c>
       <c r="AF20" s="3">
         <v>-1500</v>
       </c>
       <c r="AG20" s="3">
-        <v>-1200</v>
+        <v>-1500</v>
       </c>
       <c r="AH20" s="3">
         <v>-1200</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1954,32 +1991,35 @@
       <c r="Z21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="3">
         <v>700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>600</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>700</v>
       </c>
       <c r="AD21" s="3">
         <v>700</v>
       </c>
       <c r="AE21" s="3">
+        <v>700</v>
+      </c>
+      <c r="AF21" s="3">
         <v>600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2076,106 +2116,112 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>400</v>
+      </c>
+      <c r="E23" s="3">
         <v>300</v>
-      </c>
-      <c r="E23" s="3">
-        <v>700</v>
       </c>
       <c r="F23" s="3">
         <v>700</v>
       </c>
       <c r="G23" s="3">
+        <v>700</v>
+      </c>
+      <c r="H23" s="3">
         <v>600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2200</v>
-      </c>
-      <c r="K23" s="3">
-        <v>1200</v>
       </c>
       <c r="L23" s="3">
         <v>1200</v>
       </c>
       <c r="M23" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N23" s="3">
         <v>1100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>1100</v>
       </c>
       <c r="R23" s="3">
         <v>1100</v>
       </c>
       <c r="S23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T23" s="3">
         <v>100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>700</v>
-      </c>
-      <c r="V23" s="3">
-        <v>600</v>
       </c>
       <c r="W23" s="3">
         <v>600</v>
       </c>
       <c r="X23" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="Y23" s="3">
         <v>800</v>
       </c>
       <c r="Z23" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA23" s="3">
         <v>500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>500</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>600</v>
       </c>
       <c r="AD23" s="3">
         <v>600</v>
       </c>
       <c r="AE23" s="3">
+        <v>600</v>
+      </c>
+      <c r="AF23" s="3">
         <v>500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>300</v>
-      </c>
-      <c r="AG23" s="3">
-        <v>600</v>
       </c>
       <c r="AH23" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2183,7 +2229,7 @@
         <v>100</v>
       </c>
       <c r="E24" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F24" s="3">
         <v>200</v>
@@ -2195,49 +2241,49 @@
         <v>200</v>
       </c>
       <c r="I24" s="3">
+        <v>200</v>
+      </c>
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>400</v>
-      </c>
-      <c r="M24" s="3">
-        <v>300</v>
       </c>
       <c r="N24" s="3">
         <v>300</v>
       </c>
       <c r="O24" s="3">
+        <v>300</v>
+      </c>
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>300</v>
       </c>
       <c r="R24" s="3">
         <v>300</v>
       </c>
       <c r="S24" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="T24" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="U24" s="3">
         <v>200</v>
       </c>
       <c r="V24" s="3">
+        <v>200</v>
+      </c>
+      <c r="W24" s="3">
         <v>100</v>
-      </c>
-      <c r="W24" s="3">
-        <v>200</v>
       </c>
       <c r="X24" s="3">
         <v>200</v>
@@ -2246,16 +2292,16 @@
         <v>200</v>
       </c>
       <c r="Z24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA24" s="3">
         <v>100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1000</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>200</v>
       </c>
       <c r="AD24" s="3">
         <v>200</v>
@@ -2264,16 +2310,19 @@
         <v>200</v>
       </c>
       <c r="AF24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG24" s="3">
         <v>100</v>
-      </c>
-      <c r="AG24" s="3">
-        <v>200</v>
       </c>
       <c r="AH24" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,49 +2419,52 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>300</v>
+      </c>
+      <c r="E26" s="3">
         <v>200</v>
-      </c>
-      <c r="E26" s="3">
-        <v>500</v>
       </c>
       <c r="F26" s="3">
         <v>500</v>
       </c>
       <c r="G26" s="3">
+        <v>500</v>
+      </c>
+      <c r="H26" s="3">
         <v>400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>900</v>
-      </c>
-      <c r="L26" s="3">
-        <v>800</v>
       </c>
       <c r="M26" s="3">
         <v>800</v>
       </c>
       <c r="N26" s="3">
+        <v>800</v>
+      </c>
+      <c r="O26" s="3">
         <v>700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>600</v>
-      </c>
-      <c r="P26" s="3">
-        <v>800</v>
       </c>
       <c r="Q26" s="3">
         <v>800</v>
@@ -2421,96 +2473,99 @@
         <v>800</v>
       </c>
       <c r="S26" s="3">
+        <v>800</v>
+      </c>
+      <c r="T26" s="3">
         <v>100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>500</v>
-      </c>
-      <c r="V26" s="3">
-        <v>400</v>
       </c>
       <c r="W26" s="3">
         <v>400</v>
       </c>
       <c r="X26" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="Y26" s="3">
         <v>600</v>
       </c>
       <c r="Z26" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA26" s="3">
         <v>400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-500</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>500</v>
       </c>
       <c r="AD26" s="3">
         <v>500</v>
       </c>
       <c r="AE26" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF26" s="3">
         <v>400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>200</v>
-      </c>
-      <c r="AG26" s="3">
-        <v>400</v>
       </c>
       <c r="AH26" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>300</v>
+      </c>
+      <c r="E27" s="3">
         <v>200</v>
-      </c>
-      <c r="E27" s="3">
-        <v>500</v>
       </c>
       <c r="F27" s="3">
         <v>500</v>
       </c>
       <c r="G27" s="3">
+        <v>500</v>
+      </c>
+      <c r="H27" s="3">
         <v>400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>900</v>
-      </c>
-      <c r="L27" s="3">
-        <v>800</v>
       </c>
       <c r="M27" s="3">
         <v>800</v>
       </c>
       <c r="N27" s="3">
+        <v>800</v>
+      </c>
+      <c r="O27" s="3">
         <v>700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>600</v>
-      </c>
-      <c r="P27" s="3">
-        <v>800</v>
       </c>
       <c r="Q27" s="3">
         <v>800</v>
@@ -2519,55 +2574,58 @@
         <v>800</v>
       </c>
       <c r="S27" s="3">
+        <v>800</v>
+      </c>
+      <c r="T27" s="3">
         <v>100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>500</v>
-      </c>
-      <c r="V27" s="3">
-        <v>400</v>
       </c>
       <c r="W27" s="3">
         <v>400</v>
       </c>
       <c r="X27" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="Y27" s="3">
         <v>600</v>
       </c>
       <c r="Z27" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA27" s="3">
         <v>400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-500</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>500</v>
       </c>
       <c r="AD27" s="3">
         <v>500</v>
       </c>
       <c r="AE27" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF27" s="3">
         <v>400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>200</v>
-      </c>
-      <c r="AG27" s="3">
-        <v>400</v>
       </c>
       <c r="AH27" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,147 +3025,153 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E32" s="3">
         <v>2000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1800</v>
-      </c>
-      <c r="F32" s="3">
-        <v>1700</v>
       </c>
       <c r="G32" s="3">
         <v>1700</v>
       </c>
       <c r="H32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I32" s="3">
         <v>1600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1600</v>
-      </c>
-      <c r="M32" s="3">
-        <v>1700</v>
       </c>
       <c r="N32" s="3">
         <v>1700</v>
       </c>
       <c r="O32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P32" s="3">
         <v>1600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1800</v>
-      </c>
-      <c r="T32" s="3">
-        <v>1400</v>
       </c>
       <c r="U32" s="3">
         <v>1400</v>
       </c>
       <c r="V32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W32" s="3">
         <v>1600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1400</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>1500</v>
       </c>
       <c r="AF32" s="3">
         <v>1500</v>
       </c>
       <c r="AG32" s="3">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="AH32" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>300</v>
+      </c>
+      <c r="E33" s="3">
         <v>200</v>
-      </c>
-      <c r="E33" s="3">
-        <v>500</v>
       </c>
       <c r="F33" s="3">
         <v>500</v>
       </c>
       <c r="G33" s="3">
+        <v>500</v>
+      </c>
+      <c r="H33" s="3">
         <v>400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>900</v>
-      </c>
-      <c r="L33" s="3">
-        <v>800</v>
       </c>
       <c r="M33" s="3">
         <v>800</v>
       </c>
       <c r="N33" s="3">
+        <v>800</v>
+      </c>
+      <c r="O33" s="3">
         <v>700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>600</v>
-      </c>
-      <c r="P33" s="3">
-        <v>800</v>
       </c>
       <c r="Q33" s="3">
         <v>800</v>
@@ -3107,55 +3180,58 @@
         <v>800</v>
       </c>
       <c r="S33" s="3">
+        <v>800</v>
+      </c>
+      <c r="T33" s="3">
         <v>100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>500</v>
-      </c>
-      <c r="V33" s="3">
-        <v>400</v>
       </c>
       <c r="W33" s="3">
         <v>400</v>
       </c>
       <c r="X33" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="Y33" s="3">
         <v>600</v>
       </c>
       <c r="Z33" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA33" s="3">
         <v>400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-500</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>500</v>
       </c>
       <c r="AD33" s="3">
         <v>500</v>
       </c>
       <c r="AE33" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF33" s="3">
         <v>400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>200</v>
-      </c>
-      <c r="AG33" s="3">
-        <v>400</v>
       </c>
       <c r="AH33" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,49 +3328,52 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>300</v>
+      </c>
+      <c r="E35" s="3">
         <v>200</v>
-      </c>
-      <c r="E35" s="3">
-        <v>500</v>
       </c>
       <c r="F35" s="3">
         <v>500</v>
       </c>
       <c r="G35" s="3">
+        <v>500</v>
+      </c>
+      <c r="H35" s="3">
         <v>400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>900</v>
-      </c>
-      <c r="L35" s="3">
-        <v>800</v>
       </c>
       <c r="M35" s="3">
         <v>800</v>
       </c>
       <c r="N35" s="3">
+        <v>800</v>
+      </c>
+      <c r="O35" s="3">
         <v>700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>600</v>
-      </c>
-      <c r="P35" s="3">
-        <v>800</v>
       </c>
       <c r="Q35" s="3">
         <v>800</v>
@@ -3303,158 +3382,164 @@
         <v>800</v>
       </c>
       <c r="S35" s="3">
+        <v>800</v>
+      </c>
+      <c r="T35" s="3">
         <v>100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>500</v>
-      </c>
-      <c r="V35" s="3">
-        <v>400</v>
       </c>
       <c r="W35" s="3">
         <v>400</v>
       </c>
       <c r="X35" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="Y35" s="3">
         <v>600</v>
       </c>
       <c r="Z35" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA35" s="3">
         <v>400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-500</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>500</v>
       </c>
       <c r="AD35" s="3">
         <v>500</v>
       </c>
       <c r="AE35" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF35" s="3">
         <v>400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>200</v>
-      </c>
-      <c r="AG35" s="3">
-        <v>400</v>
       </c>
       <c r="AH35" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,204 +3611,211 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E41" s="3">
         <v>3500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4100</v>
-      </c>
-      <c r="V41" s="3">
-        <v>4500</v>
       </c>
       <c r="W41" s="3">
         <v>4500</v>
       </c>
       <c r="X41" s="3">
+        <v>4500</v>
+      </c>
+      <c r="Y41" s="3">
         <v>2400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E42" s="3">
         <v>9900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>8400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>9100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>18700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>9900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>15200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>12300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>7000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>8600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>7100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>8200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>14300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>10100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>7500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>11900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>7500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>5700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>4800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>4700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>4000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>55900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3819,8 +3912,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,8 +4013,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4015,8 +4114,11 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4113,8 +4215,11 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4211,8 +4316,11 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4220,7 +4328,7 @@
         <v>6000</v>
       </c>
       <c r="E48" s="3">
-        <v>6100</v>
+        <v>6000</v>
       </c>
       <c r="F48" s="3">
         <v>6100</v>
@@ -4229,7 +4337,7 @@
         <v>6100</v>
       </c>
       <c r="H48" s="3">
-        <v>6200</v>
+        <v>6100</v>
       </c>
       <c r="I48" s="3">
         <v>6200</v>
@@ -4238,16 +4346,16 @@
         <v>6200</v>
       </c>
       <c r="K48" s="3">
-        <v>6300</v>
+        <v>6200</v>
       </c>
       <c r="L48" s="3">
         <v>6300</v>
       </c>
       <c r="M48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="N48" s="3">
         <v>6400</v>
-      </c>
-      <c r="N48" s="3">
-        <v>6300</v>
       </c>
       <c r="O48" s="3">
         <v>6300</v>
@@ -4256,7 +4364,7 @@
         <v>6300</v>
       </c>
       <c r="Q48" s="3">
-        <v>6400</v>
+        <v>6300</v>
       </c>
       <c r="R48" s="3">
         <v>6400</v>
@@ -4265,19 +4373,19 @@
         <v>6400</v>
       </c>
       <c r="T48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="U48" s="3">
         <v>6500</v>
-      </c>
-      <c r="U48" s="3">
-        <v>6600</v>
       </c>
       <c r="V48" s="3">
         <v>6600</v>
       </c>
       <c r="W48" s="3">
+        <v>6600</v>
+      </c>
+      <c r="X48" s="3">
         <v>6700</v>
-      </c>
-      <c r="X48" s="3">
-        <v>6600</v>
       </c>
       <c r="Y48" s="3">
         <v>6600</v>
@@ -4289,13 +4397,13 @@
         <v>6600</v>
       </c>
       <c r="AB48" s="3">
-        <v>6700</v>
+        <v>6600</v>
       </c>
       <c r="AC48" s="3">
         <v>6700</v>
       </c>
       <c r="AD48" s="3">
-        <v>6800</v>
+        <v>6700</v>
       </c>
       <c r="AE48" s="3">
         <v>6800</v>
@@ -4304,13 +4412,16 @@
         <v>6800</v>
       </c>
       <c r="AG48" s="3">
-        <v>6900</v>
+        <v>6800</v>
       </c>
       <c r="AH48" s="3">
         <v>6900</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4339,7 +4450,7 @@
         <v>700</v>
       </c>
       <c r="L49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="M49" s="3">
         <v>800</v>
@@ -4372,7 +4483,7 @@
         <v>800</v>
       </c>
       <c r="W49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="X49" s="3">
         <v>900</v>
@@ -4390,7 +4501,7 @@
         <v>900</v>
       </c>
       <c r="AC49" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AD49" s="3">
         <v>1000</v>
@@ -4405,10 +4516,13 @@
         <v>1000</v>
       </c>
       <c r="AH49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AI49" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,43 +4720,46 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E52" s="3">
         <v>2800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2000</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1800</v>
       </c>
       <c r="M52" s="3">
         <v>1800</v>
       </c>
       <c r="N52" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="O52" s="3">
         <v>1700</v>
@@ -4648,19 +4768,19 @@
         <v>1700</v>
       </c>
       <c r="Q52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="R52" s="3">
         <v>1600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1700</v>
-      </c>
-      <c r="U52" s="3">
-        <v>1800</v>
       </c>
       <c r="V52" s="3">
         <v>1800</v>
@@ -4669,40 +4789,43 @@
         <v>1800</v>
       </c>
       <c r="X52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Y52" s="3">
         <v>1900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2000</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>1900</v>
       </c>
       <c r="AB52" s="3">
         <v>1900</v>
       </c>
       <c r="AC52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AD52" s="3">
         <v>2500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>357400</v>
+      </c>
+      <c r="E54" s="3">
         <v>363900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>365200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>366800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>369100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>357800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>359200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>343300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>348800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>342500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>343200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>330500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>323400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>307600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>310600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>312200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>307100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>300500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>304200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>301600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>289500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>292800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>277700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>273800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>268000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>255400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>245700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>239000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>236400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>230200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>276100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>216700</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,13 +5099,14 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E57" s="3">
         <v>300</v>
@@ -4984,16 +5115,16 @@
         <v>300</v>
       </c>
       <c r="G57" s="3">
+        <v>300</v>
+      </c>
+      <c r="H57" s="3">
         <v>200</v>
-      </c>
-      <c r="H57" s="3">
-        <v>100</v>
       </c>
       <c r="I57" s="3">
         <v>100</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -5005,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="N57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O57" s="3">
         <v>100</v>
@@ -5023,7 +5154,7 @@
         <v>100</v>
       </c>
       <c r="T57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U57" s="3">
         <v>0</v>
@@ -5067,8 +5198,11 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5165,8 +5299,11 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5263,8 +5400,11 @@
       <c r="AH59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5361,8 +5501,11 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5373,16 +5516,16 @@
         <v>1700</v>
       </c>
       <c r="F61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G61" s="3">
         <v>1900</v>
-      </c>
-      <c r="G61" s="3">
-        <v>2100</v>
       </c>
       <c r="H61" s="3">
         <v>2100</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -5459,8 +5602,11 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>314300</v>
+      </c>
+      <c r="E66" s="3">
         <v>320600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>322500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>323800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>326100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>314600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>316100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>298300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>301700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>294500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>294400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>281700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>274800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>258400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>261700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>262600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>258300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>249800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>253900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>251000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>236600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>240000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>225100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>221400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>215500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>202300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>191700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>185400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>183300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>177400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>243700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>184700</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,8 +6548,11 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6386,97 +6560,100 @@
         <v>21800</v>
       </c>
       <c r="E72" s="3">
+        <v>21800</v>
+      </c>
+      <c r="F72" s="3">
         <v>21900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>21800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>21500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>21900</v>
-      </c>
-      <c r="I72" s="3">
-        <v>21600</v>
       </c>
       <c r="J72" s="3">
         <v>21600</v>
       </c>
       <c r="K72" s="3">
+        <v>21600</v>
+      </c>
+      <c r="L72" s="3">
         <v>21100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>20500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>20100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>19500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>19000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>19500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>18800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>18300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>17800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>18900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>18500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>18100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>19100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>18900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>18500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>18000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>17800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>17700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>18300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>18000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>17700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>17500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>17200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>43200</v>
+      </c>
+      <c r="E76" s="3">
         <v>43300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>42700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>42900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>43000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>43300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>43100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>45000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>47100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>48000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>48900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>48800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>48600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>49200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>48900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>49600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>48800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>50700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>50300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>50600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>52900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>52800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>52600</v>
-      </c>
-      <c r="Z76" s="3">
-        <v>52500</v>
       </c>
       <c r="AA76" s="3">
         <v>52500</v>
       </c>
       <c r="AB76" s="3">
+        <v>52500</v>
+      </c>
+      <c r="AC76" s="3">
         <v>53100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>54000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>53700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>53100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>52700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>32400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>32000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,152 +7154,158 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>300</v>
+      </c>
+      <c r="E81" s="3">
         <v>200</v>
-      </c>
-      <c r="E81" s="3">
-        <v>500</v>
       </c>
       <c r="F81" s="3">
         <v>500</v>
       </c>
       <c r="G81" s="3">
+        <v>500</v>
+      </c>
+      <c r="H81" s="3">
         <v>400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>900</v>
-      </c>
-      <c r="L81" s="3">
-        <v>800</v>
       </c>
       <c r="M81" s="3">
         <v>800</v>
       </c>
       <c r="N81" s="3">
+        <v>800</v>
+      </c>
+      <c r="O81" s="3">
         <v>700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>600</v>
-      </c>
-      <c r="P81" s="3">
-        <v>800</v>
       </c>
       <c r="Q81" s="3">
         <v>800</v>
@@ -7119,55 +7314,58 @@
         <v>800</v>
       </c>
       <c r="S81" s="3">
+        <v>800</v>
+      </c>
+      <c r="T81" s="3">
         <v>100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>500</v>
-      </c>
-      <c r="V81" s="3">
-        <v>400</v>
       </c>
       <c r="W81" s="3">
         <v>400</v>
       </c>
       <c r="X81" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="Y81" s="3">
         <v>600</v>
       </c>
       <c r="Z81" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA81" s="3">
         <v>400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-500</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>500</v>
       </c>
       <c r="AD81" s="3">
         <v>500</v>
       </c>
       <c r="AE81" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF81" s="3">
         <v>400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>200</v>
-      </c>
-      <c r="AG81" s="3">
-        <v>400</v>
       </c>
       <c r="AH81" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7273,11 +7472,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>100</v>
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB83" s="3">
         <v>100</v>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,8 +8004,11 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7861,35 +8078,38 @@
       <c r="Y89" s="3">
         <v>0</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA89" s="3">
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB89" s="3">
         <v>1000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-200</v>
       </c>
-      <c r="AH89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7995,11 +8216,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -8022,8 +8243,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,8 +8445,11 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8289,35 +8519,38 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA94" s="3">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-13700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-10000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-7100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>45300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-57500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8430,7 +8664,7 @@
         <v>0</v>
       </c>
       <c r="AB96" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC96" s="3">
         <v>-100</v>
@@ -8442,7 +8676,7 @@
         <v>-100</v>
       </c>
       <c r="AF96" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AG96" s="3">
         <v>0</v>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,8 +8987,11 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8815,35 +9061,38 @@
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB100" s="3">
         <v>12100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>9500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>6700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>5400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-46300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>59600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,8 +9189,11 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9011,31 +9263,34 @@
       <c r="Y102" s="3">
         <v>0</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA102" s="3">
+      <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OTTW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OTTW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
   <si>
     <t>OTTW</t>
   </si>
@@ -656,252 +656,266 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3900</v>
+        <v>2400</v>
       </c>
       <c r="E8" s="3">
-        <v>3900</v>
+        <v>1900</v>
       </c>
       <c r="F8" s="3">
-        <v>3800</v>
+        <v>2500</v>
       </c>
       <c r="G8" s="3">
-        <v>3800</v>
+        <v>2600</v>
       </c>
       <c r="H8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K8" s="3">
         <v>3600</v>
       </c>
-      <c r="I8" s="3">
-        <v>3600</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>9600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>6600</v>
-      </c>
-      <c r="L8" s="3">
-        <v>3200</v>
-      </c>
-      <c r="M8" s="3">
-        <v>3100</v>
       </c>
       <c r="N8" s="3">
         <v>3200</v>
       </c>
       <c r="O8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="P8" s="3">
         <v>3200</v>
-      </c>
-      <c r="P8" s="3">
-        <v>2900</v>
       </c>
       <c r="Q8" s="3">
         <v>3200</v>
       </c>
       <c r="R8" s="3">
-        <v>3100</v>
+        <v>2900</v>
       </c>
       <c r="S8" s="3">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="T8" s="3">
         <v>3100</v>
       </c>
       <c r="U8" s="3">
-        <v>3200</v>
+        <v>3000</v>
       </c>
       <c r="V8" s="3">
         <v>3100</v>
       </c>
       <c r="W8" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="X8" s="3">
         <v>3100</v>
       </c>
       <c r="Y8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AA8" s="3">
         <v>3000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>2800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>2800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>2600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>2600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>2400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>2400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>2300</v>
-      </c>
-      <c r="AG8" s="3">
-        <v>2100</v>
-      </c>
-      <c r="AH8" s="3">
-        <v>2100</v>
       </c>
       <c r="AI8" s="3">
         <v>2100</v>
       </c>
+      <c r="AJ8" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AK8" s="3">
+        <v>2100</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1001,31 +1015,37 @@
       <c r="AI9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2700</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1102,8 +1122,14 @@
       <c r="AI10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,8 +1165,10 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1240,8 +1268,14 @@
       <c r="AI12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,31 +1375,37 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1442,8 +1482,14 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1543,8 +1589,14 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,88 +1629,90 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="E17" s="3">
-        <v>1600</v>
+        <v>2200</v>
       </c>
       <c r="F17" s="3">
-        <v>1300</v>
+        <v>2100</v>
       </c>
       <c r="G17" s="3">
-        <v>1300</v>
+        <v>2300</v>
       </c>
       <c r="H17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K17" s="3">
         <v>1200</v>
       </c>
-      <c r="I17" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>400</v>
-      </c>
-      <c r="O17" s="3">
-        <v>500</v>
-      </c>
-      <c r="P17" s="3">
-        <v>500</v>
       </c>
       <c r="Q17" s="3">
         <v>500</v>
       </c>
       <c r="R17" s="3">
+        <v>500</v>
+      </c>
+      <c r="S17" s="3">
+        <v>500</v>
+      </c>
+      <c r="T17" s="3">
         <v>600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>600</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>500</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>400</v>
       </c>
       <c r="AD17" s="3">
         <v>500</v>
@@ -1667,120 +1721,132 @@
         <v>400</v>
       </c>
       <c r="AF17" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AG17" s="3">
         <v>400</v>
       </c>
       <c r="AH17" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AI17" s="3">
         <v>400</v>
       </c>
+      <c r="AJ17" s="3">
+        <v>200</v>
+      </c>
+      <c r="AK17" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2200</v>
+        <v>300</v>
       </c>
       <c r="E18" s="3">
-        <v>2300</v>
+        <v>-200</v>
       </c>
       <c r="F18" s="3">
-        <v>2500</v>
+        <v>400</v>
       </c>
       <c r="G18" s="3">
-        <v>2500</v>
+        <v>400</v>
       </c>
       <c r="H18" s="3">
+        <v>700</v>
+      </c>
+      <c r="I18" s="3">
+        <v>800</v>
+      </c>
+      <c r="J18" s="3">
+        <v>600</v>
+      </c>
+      <c r="K18" s="3">
         <v>2400</v>
       </c>
-      <c r="I18" s="3">
-        <v>2400</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>7800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>6000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>2900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>2800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>2800</v>
-      </c>
-      <c r="O18" s="3">
-        <v>2700</v>
-      </c>
-      <c r="P18" s="3">
-        <v>2400</v>
       </c>
       <c r="Q18" s="3">
         <v>2700</v>
       </c>
       <c r="R18" s="3">
+        <v>2400</v>
+      </c>
+      <c r="S18" s="3">
+        <v>2700</v>
+      </c>
+      <c r="T18" s="3">
         <v>2500</v>
-      </c>
-      <c r="S18" s="3">
-        <v>2200</v>
-      </c>
-      <c r="T18" s="3">
-        <v>1900</v>
       </c>
       <c r="U18" s="3">
         <v>2200</v>
       </c>
       <c r="V18" s="3">
-        <v>2200</v>
+        <v>1900</v>
       </c>
       <c r="W18" s="3">
         <v>2200</v>
       </c>
       <c r="X18" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="Y18" s="3">
         <v>2200</v>
       </c>
       <c r="Z18" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="AA18" s="3">
         <v>2200</v>
       </c>
       <c r="AB18" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="AC18" s="3">
         <v>2200</v>
       </c>
       <c r="AD18" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AF18" s="3">
         <v>1900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>2000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>2000</v>
-      </c>
-      <c r="AG18" s="3">
-        <v>1700</v>
-      </c>
-      <c r="AH18" s="3">
-        <v>1900</v>
       </c>
       <c r="AI18" s="3">
         <v>1700</v>
       </c>
+      <c r="AJ18" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AK18" s="3">
+        <v>1700</v>
+      </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,132 +1882,140 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1900</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>-1800</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>-1700</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>-1700</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-5100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-3700</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-1600</v>
       </c>
       <c r="N20" s="3">
         <v>-1700</v>
       </c>
       <c r="O20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="P20" s="3">
         <v>-1700</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-1600</v>
       </c>
       <c r="Q20" s="3">
         <v>-1700</v>
       </c>
       <c r="R20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="S20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="T20" s="3">
         <v>-1400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-1200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-1800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-1400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-1400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-1600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
+      <c r="D21" s="3">
+        <v>300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F21" s="3">
+        <v>400</v>
+      </c>
+      <c r="G21" s="3">
+        <v>300</v>
+      </c>
+      <c r="H21" s="3">
+        <v>700</v>
+      </c>
+      <c r="I21" s="3">
+        <v>700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>600</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1994,55 +2068,61 @@
       <c r="AA21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB21" s="3">
-        <v>700</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>600</v>
+      <c r="AB21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD21" s="3">
         <v>700</v>
       </c>
       <c r="AE21" s="3">
+        <v>600</v>
+      </c>
+      <c r="AF21" s="3">
         <v>700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
+        <v>700</v>
+      </c>
+      <c r="AH21" s="3">
         <v>600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2119,109 +2199,121 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F23" s="3">
         <v>400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>2700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1100</v>
-      </c>
-      <c r="O23" s="3">
-        <v>1000</v>
-      </c>
-      <c r="P23" s="3">
-        <v>800</v>
       </c>
       <c r="Q23" s="3">
         <v>1000</v>
       </c>
       <c r="R23" s="3">
+        <v>800</v>
+      </c>
+      <c r="S23" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T23" s="3">
         <v>1100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>1100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>800</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>500</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>700</v>
       </c>
       <c r="AC23" s="3">
         <v>500</v>
       </c>
       <c r="AD23" s="3">
+        <v>700</v>
+      </c>
+      <c r="AE23" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF23" s="3">
         <v>600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2229,13 +2321,13 @@
         <v>100</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
-        <v>200</v>
-      </c>
       <c r="G24" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H24" s="3">
         <v>200</v>
@@ -2244,85 +2336,91 @@
         <v>200</v>
       </c>
       <c r="J24" s="3">
+        <v>200</v>
+      </c>
+      <c r="K24" s="3">
+        <v>200</v>
+      </c>
+      <c r="L24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>600</v>
-      </c>
-      <c r="L24" s="3">
-        <v>300</v>
-      </c>
-      <c r="M24" s="3">
-        <v>400</v>
       </c>
       <c r="N24" s="3">
         <v>300</v>
       </c>
       <c r="O24" s="3">
+        <v>400</v>
+      </c>
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
+        <v>300</v>
+      </c>
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>200</v>
-      </c>
-      <c r="V24" s="3">
-        <v>200</v>
-      </c>
-      <c r="W24" s="3">
-        <v>100</v>
       </c>
       <c r="X24" s="3">
         <v>200</v>
       </c>
       <c r="Y24" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z24" s="3">
         <v>200</v>
       </c>
       <c r="AA24" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB24" s="3">
         <v>200</v>
       </c>
       <c r="AC24" s="3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AD24" s="3">
         <v>200</v>
       </c>
       <c r="AE24" s="3">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AF24" s="3">
         <v>200</v>
       </c>
       <c r="AG24" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AH24" s="3">
         <v>200</v>
       </c>
       <c r="AI24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>200</v>
       </c>
+      <c r="AK24" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2520,228 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F26" s="3">
         <v>300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>500</v>
-      </c>
-      <c r="G26" s="3">
-        <v>500</v>
-      </c>
-      <c r="H26" s="3">
-        <v>400</v>
       </c>
       <c r="I26" s="3">
         <v>500</v>
       </c>
       <c r="J26" s="3">
+        <v>400</v>
+      </c>
+      <c r="K26" s="3">
+        <v>500</v>
+      </c>
+      <c r="L26" s="3">
         <v>1900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>600</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>800</v>
-      </c>
-      <c r="R26" s="3">
-        <v>800</v>
       </c>
       <c r="S26" s="3">
         <v>800</v>
       </c>
       <c r="T26" s="3">
+        <v>800</v>
+      </c>
+      <c r="U26" s="3">
+        <v>800</v>
+      </c>
+      <c r="V26" s="3">
         <v>100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>400</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>500</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>-500</v>
       </c>
       <c r="AD26" s="3">
         <v>500</v>
       </c>
       <c r="AE26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF26" s="3">
         <v>500</v>
       </c>
-      <c r="AF26" s="3">
-        <v>400</v>
-      </c>
       <c r="AG26" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AH26" s="3">
         <v>400</v>
       </c>
       <c r="AI26" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>400</v>
       </c>
+      <c r="AK26" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F27" s="3">
         <v>300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>500</v>
-      </c>
-      <c r="G27" s="3">
-        <v>500</v>
-      </c>
-      <c r="H27" s="3">
-        <v>400</v>
       </c>
       <c r="I27" s="3">
         <v>500</v>
       </c>
       <c r="J27" s="3">
+        <v>400</v>
+      </c>
+      <c r="K27" s="3">
+        <v>500</v>
+      </c>
+      <c r="L27" s="3">
         <v>1900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>600</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>800</v>
-      </c>
-      <c r="R27" s="3">
-        <v>800</v>
       </c>
       <c r="S27" s="3">
         <v>800</v>
       </c>
       <c r="T27" s="3">
+        <v>800</v>
+      </c>
+      <c r="U27" s="3">
+        <v>800</v>
+      </c>
+      <c r="V27" s="3">
         <v>100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>400</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>500</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>-500</v>
       </c>
       <c r="AD27" s="3">
         <v>500</v>
       </c>
       <c r="AE27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF27" s="3">
         <v>500</v>
       </c>
-      <c r="AF27" s="3">
-        <v>400</v>
-      </c>
       <c r="AG27" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AH27" s="3">
         <v>400</v>
       </c>
       <c r="AI27" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>400</v>
       </c>
+      <c r="AK27" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2841,14 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2948,14 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +3055,14 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3162,228 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>1700</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>1600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>5100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>3700</v>
-      </c>
-      <c r="L32" s="3">
-        <v>1700</v>
-      </c>
-      <c r="M32" s="3">
-        <v>1600</v>
       </c>
       <c r="N32" s="3">
         <v>1700</v>
       </c>
       <c r="O32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P32" s="3">
         <v>1700</v>
-      </c>
-      <c r="P32" s="3">
-        <v>1600</v>
       </c>
       <c r="Q32" s="3">
         <v>1700</v>
       </c>
       <c r="R32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="S32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="T32" s="3">
         <v>1400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>1200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>1800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>1400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>1400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>1600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>1700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>1400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>1500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>1700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>1400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>1600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>1300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>1400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>1500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>1500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>1200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F33" s="3">
         <v>300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>500</v>
-      </c>
-      <c r="G33" s="3">
-        <v>500</v>
-      </c>
-      <c r="H33" s="3">
-        <v>400</v>
       </c>
       <c r="I33" s="3">
         <v>500</v>
       </c>
       <c r="J33" s="3">
+        <v>400</v>
+      </c>
+      <c r="K33" s="3">
+        <v>500</v>
+      </c>
+      <c r="L33" s="3">
         <v>1900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>600</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>800</v>
-      </c>
-      <c r="R33" s="3">
-        <v>800</v>
       </c>
       <c r="S33" s="3">
         <v>800</v>
       </c>
       <c r="T33" s="3">
+        <v>800</v>
+      </c>
+      <c r="U33" s="3">
+        <v>800</v>
+      </c>
+      <c r="V33" s="3">
         <v>100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>400</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>500</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>-500</v>
       </c>
       <c r="AD33" s="3">
         <v>500</v>
       </c>
       <c r="AE33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF33" s="3">
         <v>500</v>
       </c>
-      <c r="AF33" s="3">
-        <v>400</v>
-      </c>
       <c r="AG33" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AH33" s="3">
         <v>400</v>
       </c>
       <c r="AI33" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>400</v>
       </c>
+      <c r="AK33" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3483,233 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F35" s="3">
         <v>300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>500</v>
-      </c>
-      <c r="G35" s="3">
-        <v>500</v>
-      </c>
-      <c r="H35" s="3">
-        <v>400</v>
       </c>
       <c r="I35" s="3">
         <v>500</v>
       </c>
       <c r="J35" s="3">
+        <v>400</v>
+      </c>
+      <c r="K35" s="3">
+        <v>500</v>
+      </c>
+      <c r="L35" s="3">
         <v>1900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>600</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>800</v>
-      </c>
-      <c r="R35" s="3">
-        <v>800</v>
       </c>
       <c r="S35" s="3">
         <v>800</v>
       </c>
       <c r="T35" s="3">
+        <v>800</v>
+      </c>
+      <c r="U35" s="3">
+        <v>800</v>
+      </c>
+      <c r="V35" s="3">
         <v>100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>400</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>500</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>-500</v>
       </c>
       <c r="AD35" s="3">
         <v>500</v>
       </c>
       <c r="AE35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF35" s="3">
         <v>500</v>
       </c>
-      <c r="AF35" s="3">
-        <v>400</v>
-      </c>
       <c r="AG35" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AH35" s="3">
         <v>400</v>
       </c>
       <c r="AI35" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>400</v>
       </c>
+      <c r="AK35" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3745,10 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,233 +3784,247 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4400</v>
+        <v>12700</v>
       </c>
       <c r="E41" s="3">
+        <v>12800</v>
+      </c>
+      <c r="F41" s="3">
+        <v>14000</v>
+      </c>
+      <c r="G41" s="3">
+        <v>13400</v>
+      </c>
+      <c r="H41" s="3">
+        <v>13000</v>
+      </c>
+      <c r="I41" s="3">
+        <v>9900</v>
+      </c>
+      <c r="J41" s="3">
+        <v>13800</v>
+      </c>
+      <c r="K41" s="3">
+        <v>10300</v>
+      </c>
+      <c r="L41" s="3">
+        <v>11400</v>
+      </c>
+      <c r="M41" s="3">
+        <v>7200</v>
+      </c>
+      <c r="N41" s="3">
+        <v>10400</v>
+      </c>
+      <c r="O41" s="3">
+        <v>5300</v>
+      </c>
+      <c r="P41" s="3">
+        <v>5600</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>5100</v>
+      </c>
+      <c r="R41" s="3">
+        <v>3400</v>
+      </c>
+      <c r="S41" s="3">
+        <v>4800</v>
+      </c>
+      <c r="T41" s="3">
+        <v>8500</v>
+      </c>
+      <c r="U41" s="3">
+        <v>9300</v>
+      </c>
+      <c r="V41" s="3">
+        <v>10700</v>
+      </c>
+      <c r="W41" s="3">
         <v>3500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="X41" s="3">
+        <v>4100</v>
+      </c>
+      <c r="Y41" s="3">
         <v>4500</v>
       </c>
-      <c r="G41" s="3">
-        <v>6300</v>
-      </c>
-      <c r="H41" s="3">
-        <v>12000</v>
-      </c>
-      <c r="I41" s="3">
-        <v>10300</v>
-      </c>
-      <c r="J41" s="3">
-        <v>11400</v>
-      </c>
-      <c r="K41" s="3">
-        <v>7200</v>
-      </c>
-      <c r="L41" s="3">
-        <v>10400</v>
-      </c>
-      <c r="M41" s="3">
-        <v>5300</v>
-      </c>
-      <c r="N41" s="3">
-        <v>5600</v>
-      </c>
-      <c r="O41" s="3">
-        <v>5100</v>
-      </c>
-      <c r="P41" s="3">
-        <v>3400</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>4800</v>
-      </c>
-      <c r="R41" s="3">
-        <v>8500</v>
-      </c>
-      <c r="S41" s="3">
-        <v>9300</v>
-      </c>
-      <c r="T41" s="3">
-        <v>10700</v>
-      </c>
-      <c r="U41" s="3">
-        <v>3500</v>
-      </c>
-      <c r="V41" s="3">
-        <v>4100</v>
-      </c>
-      <c r="W41" s="3">
+      <c r="Z41" s="3">
         <v>4500</v>
       </c>
-      <c r="X41" s="3">
-        <v>4500</v>
-      </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>2400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>3700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>4200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>2600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>2400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>2100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>2800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>3300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>3900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>3200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>300</v>
+      </c>
+      <c r="K42" s="3">
+        <v>800</v>
+      </c>
+      <c r="L42" s="3">
+        <v>9100</v>
+      </c>
+      <c r="M42" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N42" s="3">
+        <v>9300</v>
+      </c>
+      <c r="O42" s="3">
+        <v>3200</v>
+      </c>
+      <c r="P42" s="3">
+        <v>18700</v>
+      </c>
+      <c r="Q42" s="3">
         <v>9900</v>
       </c>
-      <c r="F42" s="3">
-        <v>8400</v>
-      </c>
-      <c r="G42" s="3">
-        <v>3600</v>
-      </c>
-      <c r="H42" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I42" s="3">
-        <v>800</v>
-      </c>
-      <c r="J42" s="3">
-        <v>9100</v>
-      </c>
-      <c r="K42" s="3">
-        <v>1400</v>
-      </c>
-      <c r="L42" s="3">
-        <v>9300</v>
-      </c>
-      <c r="M42" s="3">
-        <v>3200</v>
-      </c>
-      <c r="N42" s="3">
-        <v>18700</v>
-      </c>
-      <c r="O42" s="3">
-        <v>9900</v>
-      </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>15200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>12300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>7000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>8600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>7100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>8200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>14300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>10100</v>
-      </c>
-      <c r="X42" s="3">
-        <v>7500</v>
-      </c>
-      <c r="Y42" s="3">
-        <v>11900</v>
       </c>
       <c r="Z42" s="3">
         <v>7500</v>
       </c>
       <c r="AA42" s="3">
+        <v>11900</v>
+      </c>
+      <c r="AB42" s="3">
+        <v>7500</v>
+      </c>
+      <c r="AC42" s="3">
         <v>5700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>2600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>2500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>4800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>4700</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>4000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>55900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3915,31 +4101,37 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4016,31 +4208,37 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4117,31 +4315,37 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>14600</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>15700</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>15100</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>14600</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>11100</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>15200</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4218,31 +4422,37 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>18600</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>18600</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>18800</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>19400</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>20600</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>20700</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4319,79 +4529,85 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F48" s="3">
         <v>6000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>6000</v>
-      </c>
-      <c r="F48" s="3">
-        <v>6100</v>
-      </c>
-      <c r="G48" s="3">
-        <v>6100</v>
       </c>
       <c r="H48" s="3">
         <v>6100</v>
       </c>
       <c r="I48" s="3">
-        <v>6200</v>
+        <v>6100</v>
       </c>
       <c r="J48" s="3">
-        <v>6200</v>
+        <v>6100</v>
       </c>
       <c r="K48" s="3">
         <v>6200</v>
       </c>
       <c r="L48" s="3">
+        <v>6200</v>
+      </c>
+      <c r="M48" s="3">
+        <v>6200</v>
+      </c>
+      <c r="N48" s="3">
         <v>6300</v>
-      </c>
-      <c r="M48" s="3">
-        <v>6300</v>
-      </c>
-      <c r="N48" s="3">
-        <v>6400</v>
       </c>
       <c r="O48" s="3">
         <v>6300</v>
       </c>
       <c r="P48" s="3">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="Q48" s="3">
         <v>6300</v>
       </c>
       <c r="R48" s="3">
-        <v>6400</v>
+        <v>6300</v>
       </c>
       <c r="S48" s="3">
-        <v>6400</v>
+        <v>6300</v>
       </c>
       <c r="T48" s="3">
         <v>6400</v>
       </c>
       <c r="U48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="V48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="W48" s="3">
         <v>6500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>6600</v>
-      </c>
-      <c r="W48" s="3">
-        <v>6600</v>
-      </c>
-      <c r="X48" s="3">
-        <v>6700</v>
       </c>
       <c r="Y48" s="3">
         <v>6600</v>
       </c>
       <c r="Z48" s="3">
-        <v>6600</v>
+        <v>6700</v>
       </c>
       <c r="AA48" s="3">
         <v>6600</v>
@@ -4400,28 +4616,34 @@
         <v>6600</v>
       </c>
       <c r="AC48" s="3">
+        <v>6600</v>
+      </c>
+      <c r="AD48" s="3">
+        <v>6600</v>
+      </c>
+      <c r="AE48" s="3">
         <v>6700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>6700</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>6800</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>6800</v>
       </c>
       <c r="AG48" s="3">
         <v>6800</v>
       </c>
       <c r="AH48" s="3">
+        <v>6800</v>
+      </c>
+      <c r="AI48" s="3">
+        <v>6800</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>6900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4453,10 +4675,10 @@
         <v>700</v>
       </c>
       <c r="M49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="N49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="O49" s="3">
         <v>800</v>
@@ -4486,10 +4708,10 @@
         <v>800</v>
       </c>
       <c r="X49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="Y49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="Z49" s="3">
         <v>900</v>
@@ -4504,10 +4726,10 @@
         <v>900</v>
       </c>
       <c r="AD49" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AE49" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AF49" s="3">
         <v>1000</v>
@@ -4519,10 +4741,16 @@
         <v>1000</v>
       </c>
       <c r="AI49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AJ49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AK49" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4850,14 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4957,121 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>8300</v>
+      </c>
+      <c r="F52" s="3">
+        <v>8300</v>
+      </c>
+      <c r="G52" s="3">
+        <v>8400</v>
+      </c>
+      <c r="H52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="I52" s="3">
+        <v>7800</v>
+      </c>
+      <c r="J52" s="3">
+        <v>7500</v>
+      </c>
+      <c r="K52" s="3">
         <v>2700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="L52" s="3">
         <v>2800</v>
       </c>
-      <c r="F52" s="3">
-        <v>3000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>2900</v>
-      </c>
-      <c r="H52" s="3">
-        <v>2800</v>
-      </c>
-      <c r="I52" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J52" s="3">
-        <v>2800</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>2500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>2000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1800</v>
-      </c>
-      <c r="O52" s="3">
-        <v>1700</v>
-      </c>
-      <c r="P52" s="3">
-        <v>1700</v>
       </c>
       <c r="Q52" s="3">
         <v>1700</v>
       </c>
       <c r="R52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="S52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="T52" s="3">
         <v>1600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1500</v>
-      </c>
-      <c r="T52" s="3">
-        <v>1800</v>
-      </c>
-      <c r="U52" s="3">
-        <v>1700</v>
       </c>
       <c r="V52" s="3">
         <v>1800</v>
       </c>
       <c r="W52" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="X52" s="3">
         <v>1800</v>
       </c>
       <c r="Y52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AA52" s="3">
         <v>1900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>2100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>2000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>1900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>1900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>2500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>2300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>2400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>2600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>2100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5171,121 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>355200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>353200</v>
+      </c>
+      <c r="F54" s="3">
         <v>357400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>363900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>365200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>366800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>369100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>357800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>359200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>343300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>348800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>342500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>343200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>330500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>323400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>307600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>310600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>312200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>307100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>300500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>304200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>301600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>289500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>292800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>277700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>273800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>268000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>255400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>245700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>239000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>236400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>230200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>276100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>216700</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5321,10 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,38 +5360,40 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>500</v>
+        <v>275300</v>
       </c>
       <c r="E57" s="3">
-        <v>300</v>
+        <v>275000</v>
       </c>
       <c r="F57" s="3">
-        <v>300</v>
+        <v>281200</v>
       </c>
       <c r="G57" s="3">
-        <v>300</v>
+        <v>281100</v>
       </c>
       <c r="H57" s="3">
-        <v>200</v>
+        <v>284700</v>
       </c>
       <c r="I57" s="3">
+        <v>291400</v>
+      </c>
+      <c r="J57" s="3">
+        <v>295200</v>
+      </c>
+      <c r="K57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
@@ -5139,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="O57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q57" s="3">
         <v>100</v>
@@ -5157,10 +5419,10 @@
         <v>100</v>
       </c>
       <c r="U57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W57" s="3">
         <v>0</v>
@@ -5201,13 +5463,19 @@
       <c r="AI57" s="3">
         <v>0</v>
       </c>
+      <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -5302,31 +5570,37 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -5403,31 +5677,37 @@
       <c r="AI59" s="3">
         <v>0</v>
       </c>
+      <c r="AJ59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>278800</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>275700</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>281700</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>281400</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>285000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>291600</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>295400</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5504,35 +5784,41 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1700</v>
+        <v>29900</v>
       </c>
       <c r="E61" s="3">
-        <v>1700</v>
+        <v>30300</v>
       </c>
       <c r="F61" s="3">
-        <v>1700</v>
+        <v>27500</v>
       </c>
       <c r="G61" s="3">
-        <v>1900</v>
+        <v>32500</v>
       </c>
       <c r="H61" s="3">
+        <v>34500</v>
+      </c>
+      <c r="I61" s="3">
+        <v>28700</v>
+      </c>
+      <c r="J61" s="3">
+        <v>26400</v>
+      </c>
+      <c r="K61" s="3">
         <v>2100</v>
       </c>
-      <c r="I61" s="3">
-        <v>2100</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5605,31 +5891,37 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -5706,8 +5998,14 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +6105,14 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6212,14 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6319,121 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>314300</v>
+        <v>314000</v>
       </c>
       <c r="E66" s="3">
-        <v>320600</v>
+        <v>311800</v>
       </c>
       <c r="F66" s="3">
-        <v>322500</v>
+        <v>316000</v>
       </c>
       <c r="G66" s="3">
-        <v>323800</v>
+        <v>322300</v>
       </c>
       <c r="H66" s="3">
-        <v>326100</v>
+        <v>324200</v>
       </c>
       <c r="I66" s="3">
+        <v>325500</v>
+      </c>
+      <c r="J66" s="3">
+        <v>328000</v>
+      </c>
+      <c r="K66" s="3">
         <v>314600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>316100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>298300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>301700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>294500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>294400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>281700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>274800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>258400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>261700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>262600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>258300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>249800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>253900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>251000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>236600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>240000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>225100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>221400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>215500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>202300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>191700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>185400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>183300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>177400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>243700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>184700</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6469,10 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6572,14 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6679,14 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6786,14 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6893,121 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>21300</v>
+      </c>
+      <c r="F72" s="3">
         <v>21800</v>
-      </c>
-      <c r="E72" s="3">
-        <v>21800</v>
-      </c>
-      <c r="F72" s="3">
-        <v>21900</v>
       </c>
       <c r="G72" s="3">
         <v>21800</v>
       </c>
       <c r="H72" s="3">
+        <v>21900</v>
+      </c>
+      <c r="I72" s="3">
+        <v>21800</v>
+      </c>
+      <c r="J72" s="3">
         <v>21500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>21900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>21600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>21600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>21100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>20500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>20100</v>
-      </c>
-      <c r="O72" s="3">
-        <v>19500</v>
-      </c>
-      <c r="P72" s="3">
-        <v>19000</v>
       </c>
       <c r="Q72" s="3">
         <v>19500</v>
       </c>
       <c r="R72" s="3">
+        <v>19000</v>
+      </c>
+      <c r="S72" s="3">
+        <v>19500</v>
+      </c>
+      <c r="T72" s="3">
         <v>18800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>18300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>17800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>18900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>18500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>18100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>19100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>18900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>18500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>18000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>17800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>17700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>18300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>18000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>17700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>17500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>17200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +7107,14 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7214,14 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7321,121 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>43200</v>
+        <v>41200</v>
       </c>
       <c r="E76" s="3">
+        <v>41400</v>
+      </c>
+      <c r="F76" s="3">
+        <v>41500</v>
+      </c>
+      <c r="G76" s="3">
+        <v>41700</v>
+      </c>
+      <c r="H76" s="3">
+        <v>41000</v>
+      </c>
+      <c r="I76" s="3">
+        <v>41300</v>
+      </c>
+      <c r="J76" s="3">
+        <v>41200</v>
+      </c>
+      <c r="K76" s="3">
         <v>43300</v>
       </c>
-      <c r="F76" s="3">
-        <v>42700</v>
-      </c>
-      <c r="G76" s="3">
-        <v>42900</v>
-      </c>
-      <c r="H76" s="3">
-        <v>43000</v>
-      </c>
-      <c r="I76" s="3">
-        <v>43300</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>43100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>45000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>47100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>48000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>48900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>48800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>48600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>49200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>48900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>49600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>48800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>50700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>50300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>50600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>52900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>52800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>52600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>52500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>52500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>53100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>54000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>53700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>53100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>52700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>32400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>32000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7535,233 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F81" s="3">
         <v>300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>500</v>
-      </c>
-      <c r="G81" s="3">
-        <v>500</v>
-      </c>
-      <c r="H81" s="3">
-        <v>400</v>
       </c>
       <c r="I81" s="3">
         <v>500</v>
       </c>
       <c r="J81" s="3">
+        <v>400</v>
+      </c>
+      <c r="K81" s="3">
+        <v>500</v>
+      </c>
+      <c r="L81" s="3">
         <v>1900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>600</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>800</v>
-      </c>
-      <c r="R81" s="3">
-        <v>800</v>
       </c>
       <c r="S81" s="3">
         <v>800</v>
       </c>
       <c r="T81" s="3">
+        <v>800</v>
+      </c>
+      <c r="U81" s="3">
+        <v>800</v>
+      </c>
+      <c r="V81" s="3">
         <v>100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>400</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>500</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>-500</v>
       </c>
       <c r="AD81" s="3">
         <v>500</v>
       </c>
       <c r="AE81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF81" s="3">
         <v>500</v>
       </c>
-      <c r="AF81" s="3">
-        <v>400</v>
-      </c>
       <c r="AG81" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AH81" s="3">
         <v>400</v>
       </c>
       <c r="AI81" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>400</v>
       </c>
+      <c r="AK81" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,31 +7797,33 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7475,14 +7873,14 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>5</v>
+      <c r="AA83" s="3">
+        <v>0</v>
       </c>
       <c r="AB83" s="3">
-        <v>100</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD83" s="3">
         <v>100</v>
@@ -7502,8 +7900,14 @@
       <c r="AI83" s="3">
         <v>100</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +8007,14 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +8114,14 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8221,14 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8328,14 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,31 +8435,37 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -8081,35 +8515,41 @@
       <c r="Z89" s="3">
         <v>0</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>5</v>
+      <c r="AA89" s="3">
+        <v>0</v>
       </c>
       <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD89" s="3">
         <v>1000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>1400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>2400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,31 +8585,33 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8219,14 +8661,14 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>5</v>
+      <c r="AA91" s="3">
+        <v>0</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
@@ -8246,8 +8688,14 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8795,14 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,31 +8902,37 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -8522,35 +8982,41 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>5</v>
+      <c r="AA94" s="3">
+        <v>0</v>
       </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-13700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-10000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-7100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>45300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-57500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +9052,33 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8667,10 +9135,10 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD96" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE96" s="3">
         <v>-100</v>
@@ -8679,16 +9147,22 @@
         <v>-100</v>
       </c>
       <c r="AG96" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AH96" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9262,14 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9369,14 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,31 +9476,37 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -9064,58 +9556,64 @@
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>5</v>
+      <c r="AA100" s="3">
+        <v>0</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD100" s="3">
         <v>12100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>9500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>6700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>1900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>5400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-46300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>59600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9192,31 +9690,37 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -9266,31 +9770,37 @@
       <c r="Z102" s="3">
         <v>0</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>5</v>
+      <c r="AA102" s="3">
+        <v>0</v>
       </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>1500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>1900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-1600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OTTW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OTTW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
   <si>
     <t>OTTW</t>
   </si>
@@ -656,224 +656,227 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E8" s="3">
         <v>2400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2600</v>
-      </c>
-      <c r="H8" s="3">
-        <v>2800</v>
       </c>
       <c r="I8" s="3">
         <v>2800</v>
       </c>
       <c r="J8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K8" s="3">
         <v>2700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3100</v>
-      </c>
-      <c r="P8" s="3">
-        <v>3200</v>
       </c>
       <c r="Q8" s="3">
         <v>3200</v>
       </c>
       <c r="R8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="S8" s="3">
         <v>2900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3200</v>
-      </c>
-      <c r="X8" s="3">
-        <v>3100</v>
       </c>
       <c r="Y8" s="3">
         <v>3100</v>
@@ -882,31 +885,31 @@
         <v>3100</v>
       </c>
       <c r="AA8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AB8" s="3">
         <v>3000</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>2800</v>
       </c>
       <c r="AC8" s="3">
         <v>2800</v>
       </c>
       <c r="AD8" s="3">
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="AE8" s="3">
         <v>2600</v>
       </c>
       <c r="AF8" s="3">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="AG8" s="3">
         <v>2400</v>
       </c>
       <c r="AH8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AI8" s="3">
         <v>2300</v>
-      </c>
-      <c r="AI8" s="3">
-        <v>2100</v>
       </c>
       <c r="AJ8" s="3">
         <v>2100</v>
@@ -914,8 +917,11 @@
       <c r="AK8" s="3">
         <v>2100</v>
       </c>
+      <c r="AL8" s="3">
+        <v>2100</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1021,35 +1027,38 @@
       <c r="AK9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E10" s="3">
         <v>2400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2600</v>
-      </c>
-      <c r="H10" s="3">
-        <v>2800</v>
       </c>
       <c r="I10" s="3">
         <v>2800</v>
       </c>
       <c r="J10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K10" s="3">
         <v>2700</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1128,8 +1137,11 @@
       <c r="AK10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1167,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1274,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1381,8 +1397,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1407,8 +1426,8 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1488,31 +1507,34 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1595,8 +1617,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,52 +1656,53 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E17" s="3">
         <v>2100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2300</v>
-      </c>
-      <c r="H17" s="3">
-        <v>2100</v>
       </c>
       <c r="I17" s="3">
         <v>2100</v>
       </c>
       <c r="J17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K17" s="3">
         <v>2000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>600</v>
-      </c>
-      <c r="N17" s="3">
-        <v>300</v>
       </c>
       <c r="O17" s="3">
         <v>300</v>
       </c>
       <c r="P17" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q17" s="3">
         <v>400</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>500</v>
       </c>
       <c r="R17" s="3">
         <v>500</v>
@@ -1685,123 +1711,126 @@
         <v>500</v>
       </c>
       <c r="T17" s="3">
+        <v>500</v>
+      </c>
+      <c r="U17" s="3">
         <v>600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1000</v>
-      </c>
-      <c r="X17" s="3">
-        <v>900</v>
       </c>
       <c r="Y17" s="3">
         <v>900</v>
       </c>
       <c r="Z17" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="AA17" s="3">
         <v>800</v>
       </c>
       <c r="AB17" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="AC17" s="3">
         <v>600</v>
       </c>
       <c r="AD17" s="3">
+        <v>600</v>
+      </c>
+      <c r="AE17" s="3">
         <v>500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>700</v>
+      </c>
+      <c r="E18" s="3">
         <v>300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-200</v>
-      </c>
-      <c r="F18" s="3">
-        <v>400</v>
       </c>
       <c r="G18" s="3">
         <v>400</v>
       </c>
       <c r="H18" s="3">
+        <v>300</v>
+      </c>
+      <c r="I18" s="3">
         <v>700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2900</v>
-      </c>
-      <c r="O18" s="3">
-        <v>2800</v>
       </c>
       <c r="P18" s="3">
         <v>2800</v>
       </c>
       <c r="Q18" s="3">
+        <v>2800</v>
+      </c>
+      <c r="R18" s="3">
         <v>2700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1900</v>
-      </c>
-      <c r="W18" s="3">
-        <v>2200</v>
       </c>
       <c r="X18" s="3">
         <v>2200</v>
@@ -1810,10 +1839,10 @@
         <v>2200</v>
       </c>
       <c r="Z18" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AA18" s="3">
         <v>2300</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>2200</v>
       </c>
       <c r="AB18" s="3">
         <v>2200</v>
@@ -1822,31 +1851,34 @@
         <v>2200</v>
       </c>
       <c r="AD18" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AE18" s="3">
         <v>2100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1900</v>
-      </c>
-      <c r="AG18" s="3">
-        <v>2000</v>
       </c>
       <c r="AH18" s="3">
         <v>2000</v>
       </c>
       <c r="AI18" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1884,8 +1916,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1899,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -1911,115 +1944,118 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-1600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1600</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-1700</v>
       </c>
       <c r="Q20" s="3">
         <v>-1700</v>
       </c>
       <c r="R20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="S20" s="3">
         <v>-1600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-1400</v>
       </c>
       <c r="X20" s="3">
         <v>-1400</v>
       </c>
       <c r="Y20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1400</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>-1500</v>
       </c>
       <c r="AI20" s="3">
         <v>-1500</v>
       </c>
       <c r="AJ20" s="3">
-        <v>-1200</v>
+        <v>-1500</v>
       </c>
       <c r="AK20" s="3">
         <v>-1200</v>
       </c>
+      <c r="AL20" s="3">
+        <v>-1200</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="E21" s="3">
+        <v>400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>400</v>
       </c>
-      <c r="G21" s="3">
-        <v>300</v>
-      </c>
       <c r="H21" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="I21" s="3">
         <v>700</v>
       </c>
       <c r="J21" s="3">
+        <v>800</v>
+      </c>
+      <c r="K21" s="3">
         <v>600</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2074,32 +2110,35 @@
       <c r="AC21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE21" s="3">
         <v>700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>600</v>
-      </c>
-      <c r="AF21" s="3">
-        <v>700</v>
       </c>
       <c r="AG21" s="3">
         <v>700</v>
       </c>
       <c r="AH21" s="3">
+        <v>700</v>
+      </c>
+      <c r="AI21" s="3">
         <v>600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2124,8 +2163,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2205,132 +2244,138 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>700</v>
+      </c>
+      <c r="E23" s="3">
         <v>300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>300</v>
-      </c>
-      <c r="H23" s="3">
-        <v>700</v>
       </c>
       <c r="I23" s="3">
         <v>700</v>
       </c>
       <c r="J23" s="3">
+        <v>700</v>
+      </c>
+      <c r="K23" s="3">
         <v>600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2200</v>
-      </c>
-      <c r="N23" s="3">
-        <v>1200</v>
       </c>
       <c r="O23" s="3">
         <v>1200</v>
       </c>
       <c r="P23" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Q23" s="3">
         <v>1100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1000</v>
-      </c>
-      <c r="T23" s="3">
-        <v>1100</v>
       </c>
       <c r="U23" s="3">
         <v>1100</v>
       </c>
       <c r="V23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W23" s="3">
         <v>100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>700</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>600</v>
       </c>
       <c r="Z23" s="3">
         <v>600</v>
       </c>
       <c r="AA23" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="AB23" s="3">
         <v>800</v>
       </c>
       <c r="AC23" s="3">
+        <v>800</v>
+      </c>
+      <c r="AD23" s="3">
         <v>500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>500</v>
-      </c>
-      <c r="AF23" s="3">
-        <v>600</v>
       </c>
       <c r="AG23" s="3">
         <v>600</v>
       </c>
       <c r="AH23" s="3">
+        <v>600</v>
+      </c>
+      <c r="AI23" s="3">
         <v>500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>300</v>
-      </c>
-      <c r="AJ23" s="3">
-        <v>600</v>
       </c>
       <c r="AK23" s="3">
         <v>600</v>
       </c>
+      <c r="AL23" s="3">
+        <v>600</v>
+      </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3">
         <v>100</v>
       </c>
       <c r="H24" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I24" s="3">
         <v>200</v>
@@ -2342,49 +2387,49 @@
         <v>200</v>
       </c>
       <c r="L24" s="3">
+        <v>200</v>
+      </c>
+      <c r="M24" s="3">
         <v>700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
-      </c>
-      <c r="P24" s="3">
-        <v>300</v>
       </c>
       <c r="Q24" s="3">
         <v>300</v>
       </c>
       <c r="R24" s="3">
+        <v>300</v>
+      </c>
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
-      </c>
-      <c r="T24" s="3">
-        <v>300</v>
       </c>
       <c r="U24" s="3">
         <v>300</v>
       </c>
       <c r="V24" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="W24" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="X24" s="3">
         <v>200</v>
       </c>
       <c r="Y24" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z24" s="3">
         <v>100</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>200</v>
       </c>
       <c r="AA24" s="3">
         <v>200</v>
@@ -2393,16 +2438,16 @@
         <v>200</v>
       </c>
       <c r="AC24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD24" s="3">
         <v>100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1000</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>200</v>
       </c>
       <c r="AG24" s="3">
         <v>200</v>
@@ -2411,16 +2456,19 @@
         <v>200</v>
       </c>
       <c r="AI24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>100</v>
-      </c>
-      <c r="AJ24" s="3">
-        <v>200</v>
       </c>
       <c r="AK24" s="3">
         <v>200</v>
       </c>
+      <c r="AL24" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2526,58 +2574,61 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>500</v>
+      </c>
+      <c r="E26" s="3">
         <v>200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>200</v>
-      </c>
-      <c r="H26" s="3">
-        <v>500</v>
       </c>
       <c r="I26" s="3">
         <v>500</v>
       </c>
       <c r="J26" s="3">
+        <v>500</v>
+      </c>
+      <c r="K26" s="3">
         <v>400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>900</v>
-      </c>
-      <c r="O26" s="3">
-        <v>800</v>
       </c>
       <c r="P26" s="3">
         <v>800</v>
       </c>
       <c r="Q26" s="3">
+        <v>800</v>
+      </c>
+      <c r="R26" s="3">
         <v>700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>600</v>
-      </c>
-      <c r="S26" s="3">
-        <v>800</v>
       </c>
       <c r="T26" s="3">
         <v>800</v>
@@ -2586,105 +2637,108 @@
         <v>800</v>
       </c>
       <c r="V26" s="3">
+        <v>800</v>
+      </c>
+      <c r="W26" s="3">
         <v>100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>500</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>400</v>
       </c>
       <c r="Z26" s="3">
         <v>400</v>
       </c>
       <c r="AA26" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="AB26" s="3">
         <v>600</v>
       </c>
       <c r="AC26" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD26" s="3">
         <v>400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-500</v>
-      </c>
-      <c r="AF26" s="3">
-        <v>500</v>
       </c>
       <c r="AG26" s="3">
         <v>500</v>
       </c>
       <c r="AH26" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI26" s="3">
         <v>400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>200</v>
-      </c>
-      <c r="AJ26" s="3">
-        <v>400</v>
       </c>
       <c r="AK26" s="3">
         <v>400</v>
       </c>
+      <c r="AL26" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>500</v>
+      </c>
+      <c r="E27" s="3">
         <v>200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>200</v>
-      </c>
-      <c r="H27" s="3">
-        <v>500</v>
       </c>
       <c r="I27" s="3">
         <v>500</v>
       </c>
       <c r="J27" s="3">
+        <v>500</v>
+      </c>
+      <c r="K27" s="3">
         <v>400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>900</v>
-      </c>
-      <c r="O27" s="3">
-        <v>800</v>
       </c>
       <c r="P27" s="3">
         <v>800</v>
       </c>
       <c r="Q27" s="3">
+        <v>800</v>
+      </c>
+      <c r="R27" s="3">
         <v>700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>600</v>
-      </c>
-      <c r="S27" s="3">
-        <v>800</v>
       </c>
       <c r="T27" s="3">
         <v>800</v>
@@ -2693,55 +2747,58 @@
         <v>800</v>
       </c>
       <c r="V27" s="3">
+        <v>800</v>
+      </c>
+      <c r="W27" s="3">
         <v>100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>500</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>400</v>
       </c>
       <c r="Z27" s="3">
         <v>400</v>
       </c>
       <c r="AA27" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="AB27" s="3">
         <v>600</v>
       </c>
       <c r="AC27" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD27" s="3">
         <v>400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-500</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>500</v>
       </c>
       <c r="AG27" s="3">
         <v>500</v>
       </c>
       <c r="AH27" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI27" s="3">
         <v>400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>200</v>
-      </c>
-      <c r="AJ27" s="3">
-        <v>400</v>
       </c>
       <c r="AK27" s="3">
         <v>400</v>
       </c>
+      <c r="AL27" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2847,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2954,8 +3014,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,8 +3234,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3183,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
@@ -3195,138 +3264,141 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>1600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1600</v>
-      </c>
-      <c r="P32" s="3">
-        <v>1700</v>
       </c>
       <c r="Q32" s="3">
         <v>1700</v>
       </c>
       <c r="R32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="S32" s="3">
         <v>1600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1800</v>
-      </c>
-      <c r="W32" s="3">
-        <v>1400</v>
       </c>
       <c r="X32" s="3">
         <v>1400</v>
       </c>
       <c r="Y32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Z32" s="3">
         <v>1600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1400</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>1500</v>
       </c>
       <c r="AI32" s="3">
         <v>1500</v>
       </c>
       <c r="AJ32" s="3">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="AK32" s="3">
         <v>1200</v>
       </c>
+      <c r="AL32" s="3">
+        <v>1200</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>500</v>
+      </c>
+      <c r="E33" s="3">
         <v>200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>200</v>
-      </c>
-      <c r="H33" s="3">
-        <v>500</v>
       </c>
       <c r="I33" s="3">
         <v>500</v>
       </c>
       <c r="J33" s="3">
+        <v>500</v>
+      </c>
+      <c r="K33" s="3">
         <v>400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>900</v>
-      </c>
-      <c r="O33" s="3">
-        <v>800</v>
       </c>
       <c r="P33" s="3">
         <v>800</v>
       </c>
       <c r="Q33" s="3">
+        <v>800</v>
+      </c>
+      <c r="R33" s="3">
         <v>700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>600</v>
-      </c>
-      <c r="S33" s="3">
-        <v>800</v>
       </c>
       <c r="T33" s="3">
         <v>800</v>
@@ -3335,55 +3407,58 @@
         <v>800</v>
       </c>
       <c r="V33" s="3">
+        <v>800</v>
+      </c>
+      <c r="W33" s="3">
         <v>100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>500</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>400</v>
       </c>
       <c r="Z33" s="3">
         <v>400</v>
       </c>
       <c r="AA33" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="AB33" s="3">
         <v>600</v>
       </c>
       <c r="AC33" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD33" s="3">
         <v>400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-500</v>
-      </c>
-      <c r="AF33" s="3">
-        <v>500</v>
       </c>
       <c r="AG33" s="3">
         <v>500</v>
       </c>
       <c r="AH33" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI33" s="3">
         <v>400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>200</v>
-      </c>
-      <c r="AJ33" s="3">
-        <v>400</v>
       </c>
       <c r="AK33" s="3">
         <v>400</v>
       </c>
+      <c r="AL33" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,58 +3564,61 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>500</v>
+      </c>
+      <c r="E35" s="3">
         <v>200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>200</v>
-      </c>
-      <c r="H35" s="3">
-        <v>500</v>
       </c>
       <c r="I35" s="3">
         <v>500</v>
       </c>
       <c r="J35" s="3">
+        <v>500</v>
+      </c>
+      <c r="K35" s="3">
         <v>400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>900</v>
-      </c>
-      <c r="O35" s="3">
-        <v>800</v>
       </c>
       <c r="P35" s="3">
         <v>800</v>
       </c>
       <c r="Q35" s="3">
+        <v>800</v>
+      </c>
+      <c r="R35" s="3">
         <v>700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>600</v>
-      </c>
-      <c r="S35" s="3">
-        <v>800</v>
       </c>
       <c r="T35" s="3">
         <v>800</v>
@@ -3549,167 +3627,173 @@
         <v>800</v>
       </c>
       <c r="V35" s="3">
+        <v>800</v>
+      </c>
+      <c r="W35" s="3">
         <v>100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>500</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>400</v>
       </c>
       <c r="Z35" s="3">
         <v>400</v>
       </c>
       <c r="AA35" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="AB35" s="3">
         <v>600</v>
       </c>
       <c r="AC35" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD35" s="3">
         <v>400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-500</v>
-      </c>
-      <c r="AF35" s="3">
-        <v>500</v>
       </c>
       <c r="AG35" s="3">
         <v>500</v>
       </c>
       <c r="AH35" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI35" s="3">
         <v>400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>200</v>
-      </c>
-      <c r="AJ35" s="3">
-        <v>400</v>
       </c>
       <c r="AK35" s="3">
         <v>400</v>
       </c>
+      <c r="AL35" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,115 +3871,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E41" s="3">
         <v>12700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>14000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4100</v>
-      </c>
-      <c r="Y41" s="3">
-        <v>4500</v>
       </c>
       <c r="Z41" s="3">
         <v>4500</v>
       </c>
       <c r="AA41" s="3">
+        <v>4500</v>
+      </c>
+      <c r="AB41" s="3">
         <v>2400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3917,91 +4006,94 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>9100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>9300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>18700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>9900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>15200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>12300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>7000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>8600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>7100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>8200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>14300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>10100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>7500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>11900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>7500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>5700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>4800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>4700</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>55900</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4026,8 +4118,8 @@
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -4107,8 +4199,11 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4133,8 +4228,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4214,35 +4309,38 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E45" s="3">
         <v>1900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1100</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -4321,35 +4419,38 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E46" s="3">
         <v>15000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>15100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15200</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4428,35 +4529,38 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>18600</v>
+        <v>16800</v>
       </c>
       <c r="E47" s="3">
         <v>18600</v>
       </c>
       <c r="F47" s="3">
+        <v>18600</v>
+      </c>
+      <c r="G47" s="3">
         <v>18000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>18800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>19400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>20600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>20700</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -4535,25 +4639,28 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6100</v>
+        <v>6000</v>
       </c>
       <c r="E48" s="3">
         <v>6100</v>
       </c>
       <c r="F48" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="G48" s="3">
         <v>6000</v>
       </c>
       <c r="H48" s="3">
-        <v>6100</v>
+        <v>6000</v>
       </c>
       <c r="I48" s="3">
         <v>6100</v>
@@ -4562,7 +4669,7 @@
         <v>6100</v>
       </c>
       <c r="K48" s="3">
-        <v>6200</v>
+        <v>6100</v>
       </c>
       <c r="L48" s="3">
         <v>6200</v>
@@ -4571,16 +4678,16 @@
         <v>6200</v>
       </c>
       <c r="N48" s="3">
-        <v>6300</v>
+        <v>6200</v>
       </c>
       <c r="O48" s="3">
         <v>6300</v>
       </c>
       <c r="P48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="Q48" s="3">
         <v>6400</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>6300</v>
       </c>
       <c r="R48" s="3">
         <v>6300</v>
@@ -4589,7 +4696,7 @@
         <v>6300</v>
       </c>
       <c r="T48" s="3">
-        <v>6400</v>
+        <v>6300</v>
       </c>
       <c r="U48" s="3">
         <v>6400</v>
@@ -4598,19 +4705,19 @@
         <v>6400</v>
       </c>
       <c r="W48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="X48" s="3">
         <v>6500</v>
-      </c>
-      <c r="X48" s="3">
-        <v>6600</v>
       </c>
       <c r="Y48" s="3">
         <v>6600</v>
       </c>
       <c r="Z48" s="3">
+        <v>6600</v>
+      </c>
+      <c r="AA48" s="3">
         <v>6700</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>6600</v>
       </c>
       <c r="AB48" s="3">
         <v>6600</v>
@@ -4622,13 +4729,13 @@
         <v>6600</v>
       </c>
       <c r="AE48" s="3">
-        <v>6700</v>
+        <v>6600</v>
       </c>
       <c r="AF48" s="3">
         <v>6700</v>
       </c>
       <c r="AG48" s="3">
-        <v>6800</v>
+        <v>6700</v>
       </c>
       <c r="AH48" s="3">
         <v>6800</v>
@@ -4637,18 +4744,21 @@
         <v>6800</v>
       </c>
       <c r="AJ48" s="3">
-        <v>6900</v>
+        <v>6800</v>
       </c>
       <c r="AK48" s="3">
         <v>6900</v>
       </c>
+      <c r="AL48" s="3">
+        <v>6900</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E49" s="3">
         <v>700</v>
@@ -4660,7 +4770,7 @@
         <v>700</v>
       </c>
       <c r="H49" s="3">
-        <v>700</v>
+        <v>1900</v>
       </c>
       <c r="I49" s="3">
         <v>700</v>
@@ -4681,7 +4791,7 @@
         <v>700</v>
       </c>
       <c r="O49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="P49" s="3">
         <v>800</v>
@@ -4714,7 +4824,7 @@
         <v>800</v>
       </c>
       <c r="Z49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AA49" s="3">
         <v>900</v>
@@ -4732,7 +4842,7 @@
         <v>900</v>
       </c>
       <c r="AF49" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AG49" s="3">
         <v>1000</v>
@@ -4747,10 +4857,13 @@
         <v>1000</v>
       </c>
       <c r="AK49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AL49" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,52 +5079,55 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E52" s="3">
         <v>8400</v>
-      </c>
-      <c r="E52" s="3">
-        <v>8300</v>
       </c>
       <c r="F52" s="3">
         <v>8300</v>
       </c>
       <c r="G52" s="3">
-        <v>8400</v>
+        <v>8300</v>
       </c>
       <c r="H52" s="3">
+        <v>7100</v>
+      </c>
+      <c r="I52" s="3">
         <v>8100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2000</v>
-      </c>
-      <c r="O52" s="3">
-        <v>1800</v>
       </c>
       <c r="P52" s="3">
         <v>1800</v>
       </c>
       <c r="Q52" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="R52" s="3">
         <v>1700</v>
@@ -5017,19 +5136,19 @@
         <v>1700</v>
       </c>
       <c r="T52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="U52" s="3">
         <v>1600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1700</v>
-      </c>
-      <c r="X52" s="3">
-        <v>1800</v>
       </c>
       <c r="Y52" s="3">
         <v>1800</v>
@@ -5038,40 +5157,43 @@
         <v>1800</v>
       </c>
       <c r="AA52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AB52" s="3">
         <v>1900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2000</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>1900</v>
       </c>
       <c r="AE52" s="3">
         <v>1900</v>
       </c>
       <c r="AF52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AG52" s="3">
         <v>2500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>353700</v>
+      </c>
+      <c r="E54" s="3">
         <v>355200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>353200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>357400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>363900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>365200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>366800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>369100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>357800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>359200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>343300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>348800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>342500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>343200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>330500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>323400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>307600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>310600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>312200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>307100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>300500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>304200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>301600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>289500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>292800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>277700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>273800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>268000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>255400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>245700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>239000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>236400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>230200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>276100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>216700</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,40 +5491,41 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>282900</v>
+      </c>
+      <c r="E57" s="3">
         <v>275300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>275000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>281200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>281100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>284700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>291400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>295200</v>
-      </c>
-      <c r="K57" s="3">
-        <v>100</v>
       </c>
       <c r="L57" s="3">
         <v>100</v>
       </c>
       <c r="M57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N57" s="3">
         <v>0</v>
@@ -5407,7 +5537,7 @@
         <v>0</v>
       </c>
       <c r="Q57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R57" s="3">
         <v>100</v>
@@ -5425,7 +5555,7 @@
         <v>100</v>
       </c>
       <c r="W57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X57" s="3">
         <v>0</v>
@@ -5469,17 +5599,20 @@
       <c r="AK57" s="3">
         <v>0</v>
       </c>
+      <c r="AL57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>2800</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
@@ -5487,7 +5620,7 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -5576,8 +5709,11 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5602,8 +5738,8 @@
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -5683,35 +5819,38 @@
       <c r="AK59" s="3">
         <v>0</v>
       </c>
+      <c r="AL59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>283800</v>
+      </c>
+      <c r="E60" s="3">
         <v>278800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>275700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>281700</v>
       </c>
-      <c r="G60" s="3">
-        <v>281400</v>
-      </c>
       <c r="H60" s="3">
+        <v>294400</v>
+      </c>
+      <c r="I60" s="3">
         <v>285000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>291600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>295400</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5790,38 +5929,41 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E61" s="3">
         <v>29900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>30300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>27500</v>
       </c>
-      <c r="G61" s="3">
-        <v>32500</v>
-      </c>
       <c r="H61" s="3">
+        <v>19500</v>
+      </c>
+      <c r="I61" s="3">
         <v>34500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>28700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>26400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2100</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5897,35 +6039,38 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6800</v>
       </c>
-      <c r="G62" s="3">
-        <v>8400</v>
-      </c>
       <c r="H62" s="3">
+        <v>8100</v>
+      </c>
+      <c r="I62" s="3">
         <v>4800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6200</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -6004,8 +6149,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6218,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>313500</v>
+      </c>
+      <c r="E66" s="3">
         <v>314000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>311800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>316000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>322300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>324200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>325500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>328000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>314600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>316100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>298300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>301700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>294500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>294400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>281700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>274800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>258400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>261700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>262600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>258300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>249800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>253900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>251000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>236600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>240000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>225100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>221400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>215500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>202300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>191700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>185400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>183300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>177400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>243700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>184700</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6792,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E72" s="3">
         <v>21200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>21300</v>
-      </c>
-      <c r="F72" s="3">
-        <v>21800</v>
       </c>
       <c r="G72" s="3">
         <v>21800</v>
       </c>
       <c r="H72" s="3">
+        <v>21800</v>
+      </c>
+      <c r="I72" s="3">
         <v>21900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>21800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>21500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>21900</v>
-      </c>
-      <c r="L72" s="3">
-        <v>21600</v>
       </c>
       <c r="M72" s="3">
         <v>21600</v>
       </c>
       <c r="N72" s="3">
+        <v>21600</v>
+      </c>
+      <c r="O72" s="3">
         <v>21100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>20500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>20100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>19500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>19000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>19500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>18800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>18300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>17800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>18900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>18500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>18100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>19100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>18900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>18500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>18000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>17800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>17700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>18300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>18000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>17700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>17500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>17200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>40200</v>
+      </c>
+      <c r="E76" s="3">
         <v>41200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>41400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>41500</v>
       </c>
-      <c r="G76" s="3">
-        <v>41700</v>
-      </c>
       <c r="H76" s="3">
+        <v>41600</v>
+      </c>
+      <c r="I76" s="3">
         <v>41000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>41300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>41200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>43300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>43100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>45000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>47100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>48000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>48900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>48800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>48600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>49200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>48900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>49600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>48800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>50700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>50300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>50600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>52900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>52800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>52600</v>
-      </c>
-      <c r="AC76" s="3">
-        <v>52500</v>
       </c>
       <c r="AD76" s="3">
         <v>52500</v>
       </c>
       <c r="AE76" s="3">
+        <v>52500</v>
+      </c>
+      <c r="AF76" s="3">
         <v>53100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>54000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>53700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>53100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>52700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>32400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>32000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,170 +7729,176 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>500</v>
+      </c>
+      <c r="E81" s="3">
         <v>200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>200</v>
-      </c>
-      <c r="H81" s="3">
-        <v>500</v>
       </c>
       <c r="I81" s="3">
         <v>500</v>
       </c>
       <c r="J81" s="3">
+        <v>500</v>
+      </c>
+      <c r="K81" s="3">
         <v>400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>900</v>
-      </c>
-      <c r="O81" s="3">
-        <v>800</v>
       </c>
       <c r="P81" s="3">
         <v>800</v>
       </c>
       <c r="Q81" s="3">
+        <v>800</v>
+      </c>
+      <c r="R81" s="3">
         <v>700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>600</v>
-      </c>
-      <c r="S81" s="3">
-        <v>800</v>
       </c>
       <c r="T81" s="3">
         <v>800</v>
@@ -7713,55 +7907,58 @@
         <v>800</v>
       </c>
       <c r="V81" s="3">
+        <v>800</v>
+      </c>
+      <c r="W81" s="3">
         <v>100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>500</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>400</v>
       </c>
       <c r="Z81" s="3">
         <v>400</v>
       </c>
       <c r="AA81" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="AB81" s="3">
         <v>600</v>
       </c>
       <c r="AC81" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD81" s="3">
         <v>400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-500</v>
-      </c>
-      <c r="AF81" s="3">
-        <v>500</v>
       </c>
       <c r="AG81" s="3">
         <v>500</v>
       </c>
       <c r="AH81" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI81" s="3">
         <v>400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>200</v>
-      </c>
-      <c r="AJ81" s="3">
-        <v>400</v>
       </c>
       <c r="AK81" s="3">
         <v>400</v>
       </c>
+      <c r="AL81" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,8 +7996,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7825,8 +8023,8 @@
       <c r="J83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -7879,11 +8077,11 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>100</v>
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE83" s="3">
         <v>100</v>
@@ -7906,8 +8104,11 @@
       <c r="AK83" s="3">
         <v>100</v>
       </c>
+      <c r="AL83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,8 +8654,11 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8467,8 +8683,8 @@
       <c r="J89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
+      <c r="K89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
@@ -8521,35 +8737,38 @@
       <c r="AB89" s="3">
         <v>0</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD89" s="3">
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE89" s="3">
         <v>1000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,8 +8806,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8613,8 +8833,8 @@
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -8667,11 +8887,11 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE91" s="3">
         <v>0</v>
@@ -8694,8 +8914,11 @@
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,8 +9134,11 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8934,8 +9163,8 @@
       <c r="J94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -8988,35 +9217,38 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD94" s="3">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-13700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-10000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-7100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>45300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-57500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9080,8 +9313,8 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -9141,7 +9374,7 @@
         <v>0</v>
       </c>
       <c r="AE96" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF96" s="3">
         <v>-100</v>
@@ -9153,7 +9386,7 @@
         <v>-100</v>
       </c>
       <c r="AI96" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AJ96" s="3">
         <v>0</v>
@@ -9161,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,8 +9724,11 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9508,8 +9753,8 @@
       <c r="J100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -9562,35 +9807,38 @@
       <c r="AB100" s="3">
         <v>0</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD100" s="3">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE100" s="3">
         <v>12100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>9500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>6700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>5400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-46300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>59600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9615,8 +9863,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9696,8 +9944,11 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9722,8 +9973,8 @@
       <c r="J102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
@@ -9776,31 +10027,34 @@
       <c r="AB102" s="3">
         <v>0</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD102" s="3">
+      <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE102" s="3">
         <v>-600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OTTW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OTTW_QTR_FIN.xlsx
@@ -1675,7 +1675,7 @@
         <v>2100</v>
       </c>
       <c r="H17" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="I17" s="3">
         <v>2100</v>
@@ -4758,7 +4758,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>600</v>
+        <v>1800</v>
       </c>
       <c r="E49" s="3">
         <v>700</v>
@@ -5088,7 +5088,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6500</v>
+        <v>5400</v>
       </c>
       <c r="E52" s="3">
         <v>8400</v>
@@ -5498,7 +5498,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>282900</v>
+        <v>282800</v>
       </c>
       <c r="E57" s="3">
         <v>275300</v>
@@ -5608,7 +5608,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="E58" s="3">
         <v>2800</v>
@@ -5620,7 +5620,7 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>13000</v>
+        <v>16300</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -5828,7 +5828,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>283800</v>
+        <v>286900</v>
       </c>
       <c r="E60" s="3">
         <v>278800</v>
@@ -5840,7 +5840,7 @@
         <v>281700</v>
       </c>
       <c r="H60" s="3">
-        <v>294400</v>
+        <v>297700</v>
       </c>
       <c r="I60" s="3">
         <v>285000</v>
@@ -5938,7 +5938,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>23600</v>
+        <v>20400</v>
       </c>
       <c r="E61" s="3">
         <v>29900</v>
@@ -5950,7 +5950,7 @@
         <v>27500</v>
       </c>
       <c r="H61" s="3">
-        <v>19500</v>
+        <v>16200</v>
       </c>
       <c r="I61" s="3">
         <v>34500</v>
@@ -6048,7 +6048,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>6000</v>
+        <v>5800</v>
       </c>
       <c r="E62" s="3">
         <v>5300</v>

--- a/AAII_Financials/Quarterly/OTTW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OTTW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="92">
   <si>
     <t>OTTW</t>
   </si>
@@ -656,272 +656,286 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AN102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3">
         <v>2900</v>
       </c>
-      <c r="E8" s="3">
-        <v>2400</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1900</v>
-      </c>
-      <c r="G8" s="3">
-        <v>2500</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="3">
         <v>2600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>2800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>2800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>2700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>3600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>9600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>6600</v>
-      </c>
-      <c r="O8" s="3">
-        <v>3200</v>
-      </c>
-      <c r="P8" s="3">
-        <v>3100</v>
       </c>
       <c r="Q8" s="3">
         <v>3200</v>
       </c>
       <c r="R8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="S8" s="3">
         <v>3200</v>
-      </c>
-      <c r="S8" s="3">
-        <v>2900</v>
       </c>
       <c r="T8" s="3">
         <v>3200</v>
       </c>
       <c r="U8" s="3">
-        <v>3100</v>
+        <v>2900</v>
       </c>
       <c r="V8" s="3">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="W8" s="3">
         <v>3100</v>
       </c>
       <c r="X8" s="3">
-        <v>3200</v>
+        <v>3000</v>
       </c>
       <c r="Y8" s="3">
         <v>3100</v>
       </c>
       <c r="Z8" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="AA8" s="3">
         <v>3100</v>
       </c>
       <c r="AB8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AD8" s="3">
         <v>3000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>2800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>2800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>2600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>2600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>2400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>2400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>2300</v>
-      </c>
-      <c r="AJ8" s="3">
-        <v>2100</v>
-      </c>
-      <c r="AK8" s="3">
-        <v>2100</v>
       </c>
       <c r="AL8" s="3">
         <v>2100</v>
       </c>
+      <c r="AM8" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AN8" s="3">
+        <v>2100</v>
+      </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1030,41 +1044,47 @@
       <c r="AL9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3">
         <v>2900</v>
       </c>
-      <c r="E10" s="3">
-        <v>2400</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1900</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2500</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="G10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="3">
         <v>2600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>2800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>2800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>2700</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1140,8 +1160,14 @@
       <c r="AL10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1180,8 +1206,10 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1290,8 +1318,14 @@
       <c r="AL12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,8 +1434,14 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1429,11 +1469,11 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1510,37 +1550,43 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1620,8 +1666,14 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,97 +1709,99 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>2200</v>
-      </c>
-      <c r="E17" s="3">
-        <v>2100</v>
+      <c r="D17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F17" s="3">
         <v>2200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K17" s="3">
         <v>2100</v>
       </c>
-      <c r="H17" s="3">
-        <v>2200</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="L17" s="3">
         <v>2100</v>
       </c>
-      <c r="J17" s="3">
-        <v>2100</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>400</v>
-      </c>
-      <c r="R17" s="3">
-        <v>500</v>
-      </c>
-      <c r="S17" s="3">
-        <v>500</v>
       </c>
       <c r="T17" s="3">
         <v>500</v>
       </c>
       <c r="U17" s="3">
+        <v>500</v>
+      </c>
+      <c r="V17" s="3">
+        <v>500</v>
+      </c>
+      <c r="W17" s="3">
         <v>600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>600</v>
-      </c>
-      <c r="AE17" s="3">
-        <v>500</v>
-      </c>
-      <c r="AF17" s="3">
-        <v>400</v>
       </c>
       <c r="AG17" s="3">
         <v>500</v>
@@ -1756,129 +1810,141 @@
         <v>400</v>
       </c>
       <c r="AI17" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AJ17" s="3">
         <v>400</v>
       </c>
       <c r="AK17" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AL17" s="3">
         <v>400</v>
       </c>
+      <c r="AM17" s="3">
+        <v>200</v>
+      </c>
+      <c r="AN17" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="3">
         <v>700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" s="3">
         <v>300</v>
       </c>
-      <c r="F18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G18" s="3">
-        <v>400</v>
-      </c>
-      <c r="H18" s="3">
-        <v>300</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>2400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>7800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>6000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>2900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>2800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>2800</v>
-      </c>
-      <c r="R18" s="3">
-        <v>2700</v>
-      </c>
-      <c r="S18" s="3">
-        <v>2400</v>
       </c>
       <c r="T18" s="3">
         <v>2700</v>
       </c>
       <c r="U18" s="3">
+        <v>2400</v>
+      </c>
+      <c r="V18" s="3">
+        <v>2700</v>
+      </c>
+      <c r="W18" s="3">
         <v>2500</v>
-      </c>
-      <c r="V18" s="3">
-        <v>2200</v>
-      </c>
-      <c r="W18" s="3">
-        <v>1900</v>
       </c>
       <c r="X18" s="3">
         <v>2200</v>
       </c>
       <c r="Y18" s="3">
-        <v>2200</v>
+        <v>1900</v>
       </c>
       <c r="Z18" s="3">
         <v>2200</v>
       </c>
       <c r="AA18" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="AB18" s="3">
         <v>2200</v>
       </c>
       <c r="AC18" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="AD18" s="3">
         <v>2200</v>
       </c>
       <c r="AE18" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="AF18" s="3">
         <v>2200</v>
       </c>
       <c r="AG18" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AI18" s="3">
         <v>1900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>2000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>2000</v>
-      </c>
-      <c r="AJ18" s="3">
-        <v>1700</v>
-      </c>
-      <c r="AK18" s="3">
-        <v>1900</v>
       </c>
       <c r="AL18" s="3">
         <v>1700</v>
       </c>
+      <c r="AM18" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AN18" s="3">
+        <v>1700</v>
+      </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,28 +1983,30 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1947,121 +2015,127 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-1600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-5100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-3700</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-1600</v>
       </c>
       <c r="Q20" s="3">
         <v>-1700</v>
       </c>
       <c r="R20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="S20" s="3">
         <v>-1700</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-1600</v>
       </c>
       <c r="T20" s="3">
         <v>-1700</v>
       </c>
       <c r="U20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="V20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="W20" s="3">
         <v>-1400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-1200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-1800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>400</v>
       </c>
-      <c r="F21" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G21" s="3">
-        <v>400</v>
-      </c>
-      <c r="H21" s="3">
-        <v>400</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>600</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2113,32 +2187,38 @@
       <c r="AD21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE21" s="3">
-        <v>700</v>
-      </c>
-      <c r="AF21" s="3">
-        <v>600</v>
+      <c r="AE21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF21" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AG21" s="3">
         <v>700</v>
       </c>
       <c r="AH21" s="3">
+        <v>600</v>
+      </c>
+      <c r="AI21" s="3">
         <v>700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
+        <v>700</v>
+      </c>
+      <c r="AK21" s="3">
         <v>600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2166,11 +2246,11 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2247,141 +2327,153 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="3">
         <v>700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J23" s="3">
         <v>300</v>
       </c>
-      <c r="F23" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G23" s="3">
-        <v>400</v>
-      </c>
-      <c r="H23" s="3">
-        <v>300</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>2700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>2200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>1200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1100</v>
-      </c>
-      <c r="R23" s="3">
-        <v>1000</v>
-      </c>
-      <c r="S23" s="3">
-        <v>800</v>
       </c>
       <c r="T23" s="3">
         <v>1000</v>
       </c>
       <c r="U23" s="3">
+        <v>800</v>
+      </c>
+      <c r="V23" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W23" s="3">
         <v>1100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>1100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>800</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>500</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>700</v>
       </c>
       <c r="AF23" s="3">
         <v>500</v>
       </c>
       <c r="AG23" s="3">
+        <v>700</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI23" s="3">
         <v>600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>100</v>
-      </c>
-      <c r="H24" s="3">
-        <v>100</v>
-      </c>
-      <c r="I24" s="3">
-        <v>200</v>
-      </c>
-      <c r="J24" s="3">
-        <v>200</v>
       </c>
       <c r="K24" s="3">
         <v>200</v>
@@ -2390,85 +2482,91 @@
         <v>200</v>
       </c>
       <c r="M24" s="3">
+        <v>200</v>
+      </c>
+      <c r="N24" s="3">
+        <v>200</v>
+      </c>
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>600</v>
-      </c>
-      <c r="O24" s="3">
-        <v>300</v>
-      </c>
-      <c r="P24" s="3">
-        <v>400</v>
       </c>
       <c r="Q24" s="3">
         <v>300</v>
       </c>
       <c r="R24" s="3">
+        <v>400</v>
+      </c>
+      <c r="S24" s="3">
         <v>300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
+        <v>300</v>
+      </c>
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>300</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>200</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>200</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>100</v>
       </c>
       <c r="AA24" s="3">
         <v>200</v>
       </c>
       <c r="AB24" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC24" s="3">
         <v>200</v>
       </c>
       <c r="AD24" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AE24" s="3">
         <v>200</v>
       </c>
       <c r="AF24" s="3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AG24" s="3">
         <v>200</v>
       </c>
       <c r="AH24" s="3">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AI24" s="3">
         <v>200</v>
       </c>
       <c r="AJ24" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AK24" s="3">
         <v>200</v>
       </c>
       <c r="AL24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AM24" s="3">
         <v>200</v>
       </c>
+      <c r="AN24" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2675,246 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3">
         <v>500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J26" s="3">
         <v>200</v>
       </c>
-      <c r="F26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G26" s="3">
-        <v>300</v>
-      </c>
-      <c r="H26" s="3">
-        <v>200</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>500</v>
-      </c>
-      <c r="J26" s="3">
-        <v>500</v>
-      </c>
-      <c r="K26" s="3">
-        <v>400</v>
       </c>
       <c r="L26" s="3">
         <v>500</v>
       </c>
       <c r="M26" s="3">
+        <v>400</v>
+      </c>
+      <c r="N26" s="3">
+        <v>500</v>
+      </c>
+      <c r="O26" s="3">
         <v>1900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>1600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>600</v>
-      </c>
-      <c r="T26" s="3">
-        <v>800</v>
-      </c>
-      <c r="U26" s="3">
-        <v>800</v>
       </c>
       <c r="V26" s="3">
         <v>800</v>
       </c>
       <c r="W26" s="3">
+        <v>800</v>
+      </c>
+      <c r="X26" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y26" s="3">
         <v>100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>400</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>500</v>
-      </c>
-      <c r="AF26" s="3">
-        <v>-500</v>
       </c>
       <c r="AG26" s="3">
         <v>500</v>
       </c>
       <c r="AH26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AI26" s="3">
         <v>500</v>
       </c>
-      <c r="AI26" s="3">
-        <v>400</v>
-      </c>
       <c r="AJ26" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AK26" s="3">
         <v>400</v>
       </c>
       <c r="AL26" s="3">
+        <v>200</v>
+      </c>
+      <c r="AM26" s="3">
         <v>400</v>
       </c>
+      <c r="AN26" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="3">
         <v>500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27" s="3">
         <v>200</v>
       </c>
-      <c r="F27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G27" s="3">
-        <v>300</v>
-      </c>
-      <c r="H27" s="3">
-        <v>200</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>500</v>
-      </c>
-      <c r="J27" s="3">
-        <v>500</v>
-      </c>
-      <c r="K27" s="3">
-        <v>400</v>
       </c>
       <c r="L27" s="3">
         <v>500</v>
       </c>
       <c r="M27" s="3">
+        <v>400</v>
+      </c>
+      <c r="N27" s="3">
+        <v>500</v>
+      </c>
+      <c r="O27" s="3">
         <v>1900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>1600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>600</v>
-      </c>
-      <c r="T27" s="3">
-        <v>800</v>
-      </c>
-      <c r="U27" s="3">
-        <v>800</v>
       </c>
       <c r="V27" s="3">
         <v>800</v>
       </c>
       <c r="W27" s="3">
+        <v>800</v>
+      </c>
+      <c r="X27" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y27" s="3">
         <v>100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>400</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>500</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>-500</v>
       </c>
       <c r="AG27" s="3">
         <v>500</v>
       </c>
       <c r="AH27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AI27" s="3">
         <v>500</v>
       </c>
-      <c r="AI27" s="3">
-        <v>400</v>
-      </c>
       <c r="AJ27" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AK27" s="3">
         <v>400</v>
       </c>
       <c r="AL27" s="3">
+        <v>200</v>
+      </c>
+      <c r="AM27" s="3">
         <v>400</v>
       </c>
+      <c r="AN27" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +3023,14 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3017,8 +3139,14 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3255,14 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,28 +3371,34 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -3267,198 +3407,210 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>1600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>5100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>3700</v>
-      </c>
-      <c r="O32" s="3">
-        <v>1700</v>
-      </c>
-      <c r="P32" s="3">
-        <v>1600</v>
       </c>
       <c r="Q32" s="3">
         <v>1700</v>
       </c>
       <c r="R32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="S32" s="3">
         <v>1700</v>
-      </c>
-      <c r="S32" s="3">
-        <v>1600</v>
       </c>
       <c r="T32" s="3">
         <v>1700</v>
       </c>
       <c r="U32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="V32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="W32" s="3">
         <v>1400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>1200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>1800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>1400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>1400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>1600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>1700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>1400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>1500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>1700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>1400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>1600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>1300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>1400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>1500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>1200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="3">
         <v>500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J33" s="3">
         <v>200</v>
       </c>
-      <c r="F33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G33" s="3">
-        <v>300</v>
-      </c>
-      <c r="H33" s="3">
-        <v>200</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>500</v>
-      </c>
-      <c r="J33" s="3">
-        <v>500</v>
-      </c>
-      <c r="K33" s="3">
-        <v>400</v>
       </c>
       <c r="L33" s="3">
         <v>500</v>
       </c>
       <c r="M33" s="3">
+        <v>400</v>
+      </c>
+      <c r="N33" s="3">
+        <v>500</v>
+      </c>
+      <c r="O33" s="3">
         <v>1900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>1600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>600</v>
-      </c>
-      <c r="T33" s="3">
-        <v>800</v>
-      </c>
-      <c r="U33" s="3">
-        <v>800</v>
       </c>
       <c r="V33" s="3">
         <v>800</v>
       </c>
       <c r="W33" s="3">
+        <v>800</v>
+      </c>
+      <c r="X33" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y33" s="3">
         <v>100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>400</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>500</v>
-      </c>
-      <c r="AF33" s="3">
-        <v>-500</v>
       </c>
       <c r="AG33" s="3">
         <v>500</v>
       </c>
       <c r="AH33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AI33" s="3">
         <v>500</v>
       </c>
-      <c r="AI33" s="3">
-        <v>400</v>
-      </c>
       <c r="AJ33" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AK33" s="3">
         <v>400</v>
       </c>
       <c r="AL33" s="3">
+        <v>200</v>
+      </c>
+      <c r="AM33" s="3">
         <v>400</v>
       </c>
+      <c r="AN33" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3719,251 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="3">
         <v>500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J35" s="3">
         <v>200</v>
       </c>
-      <c r="F35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G35" s="3">
-        <v>300</v>
-      </c>
-      <c r="H35" s="3">
-        <v>200</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>500</v>
-      </c>
-      <c r="J35" s="3">
-        <v>500</v>
-      </c>
-      <c r="K35" s="3">
-        <v>400</v>
       </c>
       <c r="L35" s="3">
         <v>500</v>
       </c>
       <c r="M35" s="3">
+        <v>400</v>
+      </c>
+      <c r="N35" s="3">
+        <v>500</v>
+      </c>
+      <c r="O35" s="3">
         <v>1900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>1600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>600</v>
-      </c>
-      <c r="T35" s="3">
-        <v>800</v>
-      </c>
-      <c r="U35" s="3">
-        <v>800</v>
       </c>
       <c r="V35" s="3">
         <v>800</v>
       </c>
       <c r="W35" s="3">
+        <v>800</v>
+      </c>
+      <c r="X35" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y35" s="3">
         <v>100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>400</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>500</v>
-      </c>
-      <c r="AF35" s="3">
-        <v>-500</v>
       </c>
       <c r="AG35" s="3">
         <v>500</v>
       </c>
       <c r="AH35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AI35" s="3">
         <v>500</v>
       </c>
-      <c r="AI35" s="3">
-        <v>400</v>
-      </c>
       <c r="AJ35" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AK35" s="3">
         <v>400</v>
       </c>
       <c r="AL35" s="3">
+        <v>200</v>
+      </c>
+      <c r="AM35" s="3">
         <v>400</v>
       </c>
+      <c r="AN35" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +4002,10 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,118 +4044,126 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F41" s="3">
         <v>17000</v>
       </c>
-      <c r="E41" s="3">
-        <v>12700</v>
-      </c>
-      <c r="F41" s="3">
-        <v>12800</v>
-      </c>
-      <c r="G41" s="3">
-        <v>14000</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="G41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J41" s="3">
         <v>13400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>13000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>9900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>13800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>10300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>11400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>7200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>10400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>5300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>5600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>5100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>3400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>4800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>8500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>9300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>10700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>3500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>4100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>4500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>4500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>2400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>3700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>4200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>2600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>2400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>2100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>2800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>3900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>3200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4009,91 +4189,97 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>9100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>1400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>9300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>3200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>18700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>9900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>15200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>12300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>7000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>8600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>7100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>8200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>14300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>10100</v>
-      </c>
-      <c r="AA42" s="3">
-        <v>7500</v>
-      </c>
-      <c r="AB42" s="3">
-        <v>11900</v>
       </c>
       <c r="AC42" s="3">
         <v>7500</v>
       </c>
       <c r="AD42" s="3">
+        <v>11900</v>
+      </c>
+      <c r="AE42" s="3">
+        <v>7500</v>
+      </c>
+      <c r="AF42" s="3">
         <v>5700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>2600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>2500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>4800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>800</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AL42" s="3">
         <v>4000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AM42" s="3">
         <v>55900</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AN42" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4121,11 +4307,11 @@
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -4202,8 +4388,14 @@
       <c r="AL43" s="3">
         <v>0</v>
       </c>
+      <c r="AM43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4231,11 +4423,11 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4312,41 +4504,47 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3">
         <v>2100</v>
       </c>
-      <c r="E45" s="3">
-        <v>1900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K45" s="3">
         <v>1500</v>
       </c>
-      <c r="H45" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1100</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -4422,41 +4620,47 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F46" s="3">
         <v>19300</v>
       </c>
-      <c r="E46" s="3">
-        <v>15000</v>
-      </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J46" s="3">
+        <v>15100</v>
+      </c>
+      <c r="K46" s="3">
         <v>14600</v>
       </c>
-      <c r="G46" s="3">
-        <v>15700</v>
-      </c>
-      <c r="H46" s="3">
-        <v>15100</v>
-      </c>
-      <c r="I46" s="3">
-        <v>14600</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>11100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>15200</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4532,41 +4736,47 @@
       <c r="AL46" s="3">
         <v>0</v>
       </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3">
         <v>16800</v>
       </c>
-      <c r="E47" s="3">
-        <v>18600</v>
-      </c>
-      <c r="F47" s="3">
-        <v>18600</v>
-      </c>
-      <c r="G47" s="3">
-        <v>18000</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3">
         <v>18800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>19400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>20600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>20700</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -4642,88 +4852,94 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3">
         <v>6000</v>
       </c>
-      <c r="E48" s="3">
-        <v>6100</v>
-      </c>
-      <c r="F48" s="3">
-        <v>6100</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3">
         <v>6000</v>
-      </c>
-      <c r="H48" s="3">
-        <v>6000</v>
-      </c>
-      <c r="I48" s="3">
-        <v>6100</v>
-      </c>
-      <c r="J48" s="3">
-        <v>6100</v>
       </c>
       <c r="K48" s="3">
         <v>6100</v>
       </c>
       <c r="L48" s="3">
-        <v>6200</v>
+        <v>6100</v>
       </c>
       <c r="M48" s="3">
-        <v>6200</v>
+        <v>6100</v>
       </c>
       <c r="N48" s="3">
         <v>6200</v>
       </c>
       <c r="O48" s="3">
+        <v>6200</v>
+      </c>
+      <c r="P48" s="3">
+        <v>6200</v>
+      </c>
+      <c r="Q48" s="3">
         <v>6300</v>
-      </c>
-      <c r="P48" s="3">
-        <v>6300</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>6400</v>
       </c>
       <c r="R48" s="3">
         <v>6300</v>
       </c>
       <c r="S48" s="3">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="T48" s="3">
         <v>6300</v>
       </c>
       <c r="U48" s="3">
-        <v>6400</v>
+        <v>6300</v>
       </c>
       <c r="V48" s="3">
-        <v>6400</v>
+        <v>6300</v>
       </c>
       <c r="W48" s="3">
         <v>6400</v>
       </c>
       <c r="X48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="Y48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="Z48" s="3">
         <v>6500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>6600</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>6600</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>6700</v>
       </c>
       <c r="AB48" s="3">
         <v>6600</v>
       </c>
       <c r="AC48" s="3">
-        <v>6600</v>
+        <v>6700</v>
       </c>
       <c r="AD48" s="3">
         <v>6600</v>
@@ -4732,51 +4948,57 @@
         <v>6600</v>
       </c>
       <c r="AF48" s="3">
+        <v>6600</v>
+      </c>
+      <c r="AG48" s="3">
+        <v>6600</v>
+      </c>
+      <c r="AH48" s="3">
         <v>6700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>6700</v>
-      </c>
-      <c r="AH48" s="3">
-        <v>6800</v>
-      </c>
-      <c r="AI48" s="3">
-        <v>6800</v>
       </c>
       <c r="AJ48" s="3">
         <v>6800</v>
       </c>
       <c r="AK48" s="3">
+        <v>6800</v>
+      </c>
+      <c r="AL48" s="3">
+        <v>6800</v>
+      </c>
+      <c r="AM48" s="3">
         <v>6900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F49" s="3">
         <v>1800</v>
       </c>
-      <c r="E49" s="3">
-        <v>700</v>
-      </c>
-      <c r="F49" s="3">
-        <v>700</v>
-      </c>
-      <c r="G49" s="3">
-        <v>700</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="G49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J49" s="3">
         <v>1900</v>
-      </c>
-      <c r="I49" s="3">
-        <v>700</v>
-      </c>
-      <c r="J49" s="3">
-        <v>700</v>
       </c>
       <c r="K49" s="3">
         <v>700</v>
@@ -4794,10 +5016,10 @@
         <v>700</v>
       </c>
       <c r="P49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="Q49" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="R49" s="3">
         <v>800</v>
@@ -4827,10 +5049,10 @@
         <v>800</v>
       </c>
       <c r="AA49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AB49" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AC49" s="3">
         <v>900</v>
@@ -4845,10 +5067,10 @@
         <v>900</v>
       </c>
       <c r="AG49" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AH49" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AI49" s="3">
         <v>1000</v>
@@ -4860,10 +5082,16 @@
         <v>1000</v>
       </c>
       <c r="AL49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AM49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AN49" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5200,14 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,118 +5316,130 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="3">
         <v>5400</v>
       </c>
-      <c r="E52" s="3">
-        <v>8400</v>
-      </c>
-      <c r="F52" s="3">
-        <v>8300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>8300</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J52" s="3">
         <v>7100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>8100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>7800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>7500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>2700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>2800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>2500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>2000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>1800</v>
-      </c>
-      <c r="R52" s="3">
-        <v>1700</v>
-      </c>
-      <c r="S52" s="3">
-        <v>1700</v>
       </c>
       <c r="T52" s="3">
         <v>1700</v>
       </c>
       <c r="U52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="W52" s="3">
         <v>1600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1500</v>
-      </c>
-      <c r="W52" s="3">
-        <v>1800</v>
-      </c>
-      <c r="X52" s="3">
-        <v>1700</v>
       </c>
       <c r="Y52" s="3">
         <v>1800</v>
       </c>
       <c r="Z52" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="AA52" s="3">
         <v>1800</v>
       </c>
       <c r="AB52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AC52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AD52" s="3">
         <v>1900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>2100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>2000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>1900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>1900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>2500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>2300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>2600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>2100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5548,130 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F54" s="3">
         <v>353700</v>
       </c>
-      <c r="E54" s="3">
-        <v>355200</v>
-      </c>
-      <c r="F54" s="3">
-        <v>353200</v>
-      </c>
-      <c r="G54" s="3">
-        <v>357400</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J54" s="3">
         <v>363900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>365200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>366800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>369100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>357800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>359200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>343300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>348800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>342500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>343200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>330500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>323400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>307600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>310600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>312200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>307100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>300500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>304200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>301600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>289500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>292800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>277700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>273800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>268000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>255400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>245700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>239000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>236400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>230200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>276100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>216700</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5710,10 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,47 +5752,49 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" s="3">
         <v>282800</v>
       </c>
-      <c r="E57" s="3">
-        <v>275300</v>
-      </c>
-      <c r="F57" s="3">
-        <v>275000</v>
-      </c>
-      <c r="G57" s="3">
-        <v>281200</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J57" s="3">
         <v>281100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>284700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>291400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>295200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3">
-        <v>0</v>
-      </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
       <c r="P57" s="3">
         <v>0</v>
       </c>
@@ -5540,10 +5802,10 @@
         <v>0</v>
       </c>
       <c r="R57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T57" s="3">
         <v>100</v>
@@ -5558,10 +5820,10 @@
         <v>100</v>
       </c>
       <c r="X57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z57" s="3">
         <v>0</v>
@@ -5602,32 +5864,38 @@
       <c r="AL57" s="3">
         <v>0</v>
       </c>
+      <c r="AM57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F58" s="3">
         <v>3300</v>
       </c>
-      <c r="E58" s="3">
-        <v>2800</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="G58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J58" s="3">
         <v>16300</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -5712,8 +5980,14 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5741,11 +6015,11 @@
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
-      </c>
-      <c r="M59" s="3">
-        <v>0</v>
+      <c r="L59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N59" s="3">
         <v>0</v>
@@ -5822,41 +6096,47 @@
       <c r="AL59" s="3">
         <v>0</v>
       </c>
+      <c r="AM59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F60" s="3">
         <v>286900</v>
       </c>
-      <c r="E60" s="3">
-        <v>278800</v>
-      </c>
-      <c r="F60" s="3">
-        <v>275700</v>
-      </c>
-      <c r="G60" s="3">
-        <v>281700</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="G60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J60" s="3">
         <v>297700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>285000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>291600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>295400</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -5932,44 +6212,50 @@
       <c r="AL60" s="3">
         <v>0</v>
       </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>20400</v>
       </c>
-      <c r="E61" s="3">
-        <v>29900</v>
-      </c>
-      <c r="F61" s="3">
-        <v>30300</v>
-      </c>
       <c r="G61" s="3">
-        <v>27500</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>16200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>34500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>28700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>26400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2100</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -6042,41 +6328,47 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3">
         <v>5800</v>
       </c>
-      <c r="E62" s="3">
-        <v>5300</v>
-      </c>
-      <c r="F62" s="3">
-        <v>5700</v>
-      </c>
-      <c r="G62" s="3">
-        <v>6800</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J62" s="3">
         <v>8100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>4800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>5200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>6200</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -6152,8 +6444,14 @@
       <c r="AL62" s="3">
         <v>0</v>
       </c>
+      <c r="AM62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6560,14 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6676,14 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6792,130 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" s="3">
         <v>313500</v>
       </c>
-      <c r="E66" s="3">
-        <v>314000</v>
-      </c>
-      <c r="F66" s="3">
-        <v>311800</v>
-      </c>
-      <c r="G66" s="3">
-        <v>316000</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="G66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J66" s="3">
         <v>322300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>324200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>325500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>328000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>314600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>316100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>298300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>301700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>294500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>294400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>281700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>274800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>258400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>261700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>262600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>258300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>249800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>253900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>251000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>236600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>240000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>225100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>221400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>215500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>202300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>191700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>185400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>183300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>177400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>243700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>184700</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6954,10 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +7066,14 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7182,14 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7298,14 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7414,130 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F72" s="3">
         <v>21500</v>
       </c>
-      <c r="E72" s="3">
-        <v>21200</v>
-      </c>
-      <c r="F72" s="3">
-        <v>21300</v>
-      </c>
-      <c r="G72" s="3">
-        <v>21800</v>
-      </c>
-      <c r="H72" s="3">
-        <v>21800</v>
-      </c>
-      <c r="I72" s="3">
-        <v>21900</v>
+      <c r="G72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J72" s="3">
         <v>21800</v>
       </c>
       <c r="K72" s="3">
+        <v>21900</v>
+      </c>
+      <c r="L72" s="3">
+        <v>21800</v>
+      </c>
+      <c r="M72" s="3">
         <v>21500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>21900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>21600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>21600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>21100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>20500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>20100</v>
-      </c>
-      <c r="R72" s="3">
-        <v>19500</v>
-      </c>
-      <c r="S72" s="3">
-        <v>19000</v>
       </c>
       <c r="T72" s="3">
         <v>19500</v>
       </c>
       <c r="U72" s="3">
+        <v>19000</v>
+      </c>
+      <c r="V72" s="3">
+        <v>19500</v>
+      </c>
+      <c r="W72" s="3">
         <v>18800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>18300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>17800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>18900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>18500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>18100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>19100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>18900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>18500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>18000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>17800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>17700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>18300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>18000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>17700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>17500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>17200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7646,14 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7762,14 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7878,130 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F76" s="3">
         <v>40200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J76" s="3">
+        <v>41600</v>
+      </c>
+      <c r="K76" s="3">
+        <v>41000</v>
+      </c>
+      <c r="L76" s="3">
+        <v>41300</v>
+      </c>
+      <c r="M76" s="3">
         <v>41200</v>
       </c>
-      <c r="F76" s="3">
-        <v>41400</v>
-      </c>
-      <c r="G76" s="3">
-        <v>41500</v>
-      </c>
-      <c r="H76" s="3">
-        <v>41600</v>
-      </c>
-      <c r="I76" s="3">
-        <v>41000</v>
-      </c>
-      <c r="J76" s="3">
-        <v>41300</v>
-      </c>
-      <c r="K76" s="3">
-        <v>41200</v>
-      </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>43300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>43100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>45000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>47100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>48000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>48900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>48800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>48600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>49200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>48900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>49600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>48800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>50700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>50300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>50600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>52900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>52800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>52600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>52500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>52500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>53100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>54000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>53700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>53100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>52700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>32400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>32000</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +8110,251 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F81" s="3">
         <v>500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J81" s="3">
         <v>200</v>
       </c>
-      <c r="F81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G81" s="3">
-        <v>300</v>
-      </c>
-      <c r="H81" s="3">
-        <v>200</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>500</v>
-      </c>
-      <c r="J81" s="3">
-        <v>500</v>
-      </c>
-      <c r="K81" s="3">
-        <v>400</v>
       </c>
       <c r="L81" s="3">
         <v>500</v>
       </c>
       <c r="M81" s="3">
+        <v>400</v>
+      </c>
+      <c r="N81" s="3">
+        <v>500</v>
+      </c>
+      <c r="O81" s="3">
         <v>1900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>1600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>600</v>
-      </c>
-      <c r="T81" s="3">
-        <v>800</v>
-      </c>
-      <c r="U81" s="3">
-        <v>800</v>
       </c>
       <c r="V81" s="3">
         <v>800</v>
       </c>
       <c r="W81" s="3">
+        <v>800</v>
+      </c>
+      <c r="X81" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y81" s="3">
         <v>100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>400</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>500</v>
-      </c>
-      <c r="AF81" s="3">
-        <v>-500</v>
       </c>
       <c r="AG81" s="3">
         <v>500</v>
       </c>
       <c r="AH81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AI81" s="3">
         <v>500</v>
       </c>
-      <c r="AI81" s="3">
-        <v>400</v>
-      </c>
       <c r="AJ81" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AK81" s="3">
         <v>400</v>
       </c>
       <c r="AL81" s="3">
+        <v>200</v>
+      </c>
+      <c r="AM81" s="3">
         <v>400</v>
       </c>
+      <c r="AN81" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,8 +8393,10 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8026,11 +8424,11 @@
       <c r="K83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -8080,14 +8478,14 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>5</v>
+      <c r="AD83" s="3">
+        <v>0</v>
       </c>
       <c r="AE83" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="AF83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AG83" s="3">
         <v>100</v>
@@ -8107,8 +8505,14 @@
       <c r="AL83" s="3">
         <v>100</v>
       </c>
+      <c r="AM83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AN83" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8621,14 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8737,14 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8853,14 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8969,14 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,8 +9085,14 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8686,11 +9120,11 @@
       <c r="K89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N89" s="3">
         <v>0</v>
@@ -8740,35 +9174,41 @@
       <c r="AC89" s="3">
         <v>0</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>5</v>
+      <c r="AD89" s="3">
+        <v>0</v>
       </c>
       <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG89" s="3">
         <v>1000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>1400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>2400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>-200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,8 +9247,10 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8836,11 +9278,11 @@
       <c r="K91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -8890,14 +9332,14 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>5</v>
+      <c r="AD91" s="3">
+        <v>0</v>
       </c>
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
+      <c r="AF91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AG91" s="3">
         <v>0</v>
@@ -8917,8 +9359,14 @@
       <c r="AL91" s="3">
         <v>0</v>
       </c>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9475,14 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,8 +9591,14 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9166,11 +9626,11 @@
       <c r="K94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -9220,35 +9680,41 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>5</v>
+      <c r="AD94" s="3">
+        <v>0</v>
       </c>
       <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-13700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-10000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-7100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>45300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-57500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9753,10 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9316,11 +9784,11 @@
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9377,10 +9845,10 @@
         <v>0</v>
       </c>
       <c r="AF96" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AG96" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AH96" s="3">
         <v>-100</v>
@@ -9389,16 +9857,22 @@
         <v>-100</v>
       </c>
       <c r="AJ96" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AK96" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9981,14 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +10097,14 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,8 +10213,14 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9756,11 +10248,11 @@
       <c r="K100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -9810,35 +10302,41 @@
       <c r="AC100" s="3">
         <v>0</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>5</v>
+      <c r="AD100" s="3">
+        <v>0</v>
       </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG100" s="3">
         <v>12100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>9500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>6700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>1900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>5400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-46300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>59600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9866,11 +10364,11 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9947,8 +10445,14 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9976,11 +10480,11 @@
       <c r="K102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
+      <c r="L102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N102" s="3">
         <v>0</v>
@@ -10030,31 +10534,37 @@
       <c r="AC102" s="3">
         <v>0</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>5</v>
+      <c r="AD102" s="3">
+        <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG102" s="3">
         <v>-600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>1500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>1900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>-1600</v>
       </c>
     </row>
